--- a/doc/NOTES.xlsx
+++ b/doc/NOTES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MY PC\Documents\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68710CA-F815-4B3B-A6E5-1D29F4FCB42B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C9C5B2-8A67-49C6-AE6F-EA52AE9FD3BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="1011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="1041">
   <si>
     <t>HTML</t>
   </si>
@@ -153,9 +153,6 @@
   </si>
   <si>
     <t>Dropdown Menu</t>
-  </si>
-  <si>
-    <t>Supports Multi Selects</t>
   </si>
   <si>
     <t>option</t>
@@ -366,9 +363,6 @@
   </si>
   <si>
     <t>Deletion : put a line in center of content as no longer required</t>
-  </si>
-  <si>
-    <t>Insertion : underline content as inserted r</t>
   </si>
   <si>
     <t>Address</t>
@@ -6069,6 +6063,268 @@
   </si>
   <si>
     <t xml:space="preserve"> Defines a perspective view for a 3D transformed element </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supports Multi Selects inside options tag </t>
+  </si>
+  <si>
+    <t>Insertion : underline content as inserted rn</t>
+  </si>
+  <si>
+    <t>Layouts</t>
+  </si>
+  <si>
+    <t>Flexbox</t>
+  </si>
+  <si>
+    <t>Flexbox is short for the Flexible Box Layout module.</t>
+  </si>
+  <si>
+    <t>Flexbox is a layout method for arranging items in rows or columns.</t>
+  </si>
+  <si>
+    <t>Flexbox makes it easier to design a flexible, responsive layout structure without using float or positioning.</t>
+  </si>
+  <si>
+    <t>Before the Flexible Box Layout module, there were four layout modes:</t>
+  </si>
+  <si>
+    <t>Block, for sections in a webpage</t>
+  </si>
+  <si>
+    <t>Inline, for text</t>
+  </si>
+  <si>
+    <t>Table, for two-dimensional table data</t>
+  </si>
+  <si>
+    <t>Positioned, for the explicit position of an element</t>
+  </si>
+  <si>
+    <t>Flexbox One-Dimensional Layout</t>
+  </si>
+  <si>
+    <t>A Flexbox always consists of:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Flex Items - the items inside the container </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>&lt;div&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>A Flex container - the parent &lt;container&gt; &lt;div&gt; element</t>
+  </si>
+  <si>
+    <t>Flex Container properties</t>
+  </si>
+  <si>
+    <t>display: flex; or inline-flex;</t>
+  </si>
+  <si>
+    <r>
+      <t>flex-direction:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> row | row-reverse | column | column-reverse</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>flex-wrap:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nowrap | wrap | wrap-reverse</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>justify-content:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flex-start | flex-end | center | space-between | space-around | space-evenly</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>align-items:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> stretch | flex-start | flex-end | center | baseline | normal</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>align-content:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for multi-line alignment: flex-start | flex-end | center | space-between | space-around | space-evenly | stretch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>flex-flow:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> row nowrap (shorthand for flex-direction and flex-wrap)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>gap:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> spacing between items</t>
+    </r>
+  </si>
+  <si>
+    <t>flex-items properties</t>
+  </si>
+  <si>
+    <r>
+      <t>flex:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> shorthand for flex-grow, flex-shrink, flex-basis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>flex-grow:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> how much an item will grow relative to others</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>flex-shrink:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> how much it will shrink</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>flex-basis:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> default size</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>align-self:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> overrides align-items for a specific item</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>order:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> control order of appearance</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -7506,7 +7762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B8:D701"/>
+  <dimension ref="B8:D733"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="29.81640625" customWidth="1"/>
@@ -7519,7 +7775,7 @@
     <row r="9" spans="3:4" ht="18.5">
       <c r="C9" s="4"/>
       <c r="D9" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="3:4">
@@ -7527,7 +7783,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="3:4">
@@ -7535,7 +7791,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="3:4">
@@ -7543,7 +7799,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="3:4">
@@ -7551,7 +7807,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="3:4">
@@ -7559,7 +7815,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="3:4">
@@ -7567,15 +7823,15 @@
         <v>6</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="18.5">
       <c r="C17" s="14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -7583,10 +7839,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -7594,10 +7850,10 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D20" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -7605,10 +7861,10 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="2:4">
@@ -7616,10 +7872,10 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D22" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="2:4">
@@ -7627,10 +7883,10 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -7638,10 +7894,10 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D24" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="2:4">
@@ -7649,10 +7905,10 @@
         <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D25" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="2:4">
@@ -7660,10 +7916,10 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D26" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:4">
@@ -7671,10 +7927,10 @@
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="15.5">
@@ -7682,33 +7938,33 @@
         <v>10</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D29" s="4"/>
     </row>
     <row r="30" spans="2:4">
       <c r="B30" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D30" s="15" t="s">
         <v>175</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="31" spans="2:4">
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="16" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="2:4">
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="16" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="2:4">
@@ -7718,27 +7974,27 @@
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="16" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37" spans="2:4">
@@ -7748,41 +8004,41 @@
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C38" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43" spans="2:4">
@@ -7792,34 +8048,34 @@
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="2:4">
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48" spans="2:4">
@@ -7829,48 +8085,48 @@
     </row>
     <row r="49" spans="2:4">
       <c r="B49" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="50" spans="2:4">
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="51" spans="2:4">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="37" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="52" spans="2:4">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="37" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="53" spans="2:4">
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="37" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="54" spans="2:4">
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="55" spans="2:4">
@@ -7880,34 +8136,34 @@
     </row>
     <row r="56" spans="2:4">
       <c r="B56" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="D56" s="37" t="s">
         <v>398</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="D56" s="37" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="57" spans="2:4">
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="58" spans="2:4">
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="37" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="59" spans="2:4">
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="60" spans="2:4">
@@ -7920,15 +8176,15 @@
         <v>11</v>
       </c>
       <c r="C62" t="s">
+        <v>402</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>404</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="63" spans="2:4">
       <c r="D63" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="64" spans="2:4">
@@ -7936,35 +8192,35 @@
         <v>12</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D64" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="65" spans="2:4">
       <c r="D65" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="66" spans="2:4">
       <c r="D66" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="67" spans="2:4">
       <c r="D67" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="68" spans="2:4">
       <c r="D68" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="69" spans="2:4">
       <c r="D69" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="71" spans="2:4">
@@ -7972,35 +8228,35 @@
         <v>13</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D71" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="72" spans="2:4">
       <c r="D72" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="73" spans="2:4">
       <c r="D73" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="74" spans="2:4">
       <c r="D74" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="75" spans="2:4">
       <c r="D75" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="76" spans="2:4">
       <c r="D76" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="78" spans="2:4">
@@ -8008,35 +8264,35 @@
         <v>14</v>
       </c>
       <c r="C78" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D78" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="79" spans="2:4">
       <c r="D79" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="80" spans="2:4">
       <c r="D80" s="38" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="81" spans="2:4">
       <c r="D81" s="38" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="82" spans="2:4">
       <c r="D82" s="38" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="83" spans="2:4">
       <c r="D83" s="38" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="85" spans="2:4">
@@ -8044,25 +8300,25 @@
         <v>15</v>
       </c>
       <c r="C85" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D85" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="86" spans="2:4">
       <c r="D86" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="87" spans="2:4">
       <c r="D87" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="88" spans="2:4">
       <c r="D88" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="90" spans="2:4">
@@ -8070,15 +8326,15 @@
         <v>16</v>
       </c>
       <c r="C90" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D90" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="91" spans="2:4">
       <c r="D91" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="93" spans="2:4">
@@ -8086,10 +8342,10 @@
         <v>17</v>
       </c>
       <c r="C93" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D93" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="95" spans="2:4">
@@ -8097,15 +8353,15 @@
         <v>18</v>
       </c>
       <c r="C95" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D95" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="96" spans="2:4">
       <c r="D96" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="98" spans="2:4">
@@ -8113,15 +8369,15 @@
         <v>19</v>
       </c>
       <c r="C98" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D98" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="99" spans="2:4">
       <c r="D99" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="101" spans="2:4">
@@ -8129,15 +8385,15 @@
         <v>20</v>
       </c>
       <c r="C101" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D101" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="102" spans="2:4">
       <c r="D102" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="104" spans="2:4">
@@ -8145,25 +8401,25 @@
         <v>21</v>
       </c>
       <c r="C104" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D104" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="105" spans="2:4">
       <c r="D105" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="106" spans="2:4">
       <c r="D106" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="107" spans="2:4">
       <c r="D107" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="109" spans="2:4">
@@ -8171,10 +8427,10 @@
         <v>22</v>
       </c>
       <c r="C109" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D109" s="38" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="110" spans="2:4">
@@ -8182,15 +8438,15 @@
         <v>23</v>
       </c>
       <c r="C110" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D110" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="111" spans="2:4">
       <c r="D111" s="39" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="112" spans="2:4">
@@ -8198,35 +8454,35 @@
         <v>24</v>
       </c>
       <c r="C112" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D112" s="40" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="113" spans="2:4">
       <c r="D113" s="39" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="114" spans="2:4">
       <c r="D114" s="40" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="115" spans="2:4">
       <c r="D115" s="39" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="116" spans="2:4">
       <c r="D116" s="40" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="117" spans="2:4">
       <c r="D117" s="39" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="118" spans="2:4">
@@ -8237,28 +8493,28 @@
         <v>25</v>
       </c>
       <c r="C119" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D119" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="120" spans="2:4">
       <c r="D120" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="121" spans="2:4">
       <c r="C121" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D121" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="122" spans="2:4">
       <c r="D122" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="124" spans="2:4">
@@ -8266,15 +8522,15 @@
         <v>26</v>
       </c>
       <c r="C124" t="s">
+        <v>469</v>
+      </c>
+      <c r="D124" s="35" t="s">
         <v>471</v>
-      </c>
-      <c r="D124" s="35" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="125" spans="2:4">
       <c r="D125" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="126" spans="2:4">
@@ -8282,35 +8538,35 @@
         <v>27</v>
       </c>
       <c r="C126" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D126" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="127" spans="2:4">
       <c r="D127" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="128" spans="2:4">
       <c r="D128" s="41" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="129" spans="2:4">
       <c r="D129" s="41" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="130" spans="2:4">
       <c r="D130" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="131" spans="2:4">
       <c r="C131" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -8318,40 +8574,40 @@
         <v>28</v>
       </c>
       <c r="C132" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D132" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="133" spans="2:4">
       <c r="D133" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="134" spans="2:4">
       <c r="D134" s="41" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="135" spans="2:4">
       <c r="D135" s="41" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="136" spans="2:4">
       <c r="D136" s="41" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="137" spans="2:4">
       <c r="D137" s="40" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="138" spans="2:4">
       <c r="D138" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="140" spans="2:4">
@@ -8359,40 +8615,40 @@
         <v>29</v>
       </c>
       <c r="C140" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D140" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="141" spans="2:4">
       <c r="D141" s="36" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="142" spans="2:4">
       <c r="D142" s="36" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="143" spans="2:4">
       <c r="D143" s="36" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="144" spans="2:4">
       <c r="D144" s="36" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="145" spans="2:4">
       <c r="D145" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="146" spans="2:4">
       <c r="D146" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -8400,101 +8656,101 @@
         <v>30</v>
       </c>
       <c r="C148" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D148" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="D149" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="150" spans="2:4">
       <c r="C150" s="36" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D150" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="151" spans="2:4">
       <c r="D151" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="152" spans="2:4">
       <c r="D152" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="D153" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="D154" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="155" spans="2:4">
       <c r="D155" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="156" spans="2:4">
       <c r="D156" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="D157" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="158" spans="2:4">
       <c r="D158" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="159" spans="2:4">
       <c r="D159" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="C161" s="36" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="D162" s="39" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="163" spans="2:4">
       <c r="D163" s="39" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="164" spans="2:4">
       <c r="D164" s="39" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="165" spans="2:4">
       <c r="D165" s="39" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="166" spans="2:4">
       <c r="D166" s="39" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="167" spans="2:4">
@@ -8502,25 +8758,25 @@
     </row>
     <row r="168" spans="2:4">
       <c r="C168" s="36" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D168" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="D169" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="D170" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="171" spans="2:4">
       <c r="D171" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -8528,15 +8784,15 @@
         <v>31</v>
       </c>
       <c r="C173" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D173" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="174" spans="2:4">
       <c r="D174" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="176" spans="2:4">
@@ -8544,35 +8800,35 @@
         <v>32</v>
       </c>
       <c r="C176" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D176" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="177" spans="2:4">
       <c r="D177" s="39" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="178" spans="2:4">
       <c r="D178" s="39" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="179" spans="2:4">
       <c r="D179" s="39" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="180" spans="2:4">
       <c r="D180" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="181" spans="2:4">
       <c r="D181" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="183" spans="2:4">
@@ -8580,10 +8836,10 @@
         <v>33</v>
       </c>
       <c r="C183" s="36" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D183" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="185" spans="2:4" ht="28">
@@ -8591,72 +8847,72 @@
         <v>34</v>
       </c>
       <c r="C185" s="42" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D185" s="44" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="186" spans="2:4">
       <c r="C186" s="43"/>
       <c r="D186" s="44" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="187" spans="2:4">
       <c r="C187" s="43"/>
       <c r="D187" s="44" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="188" spans="2:4">
       <c r="D188" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="189" spans="2:4">
       <c r="D189" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="190" spans="2:4">
       <c r="D190" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="191" spans="2:4">
       <c r="D191" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="192" spans="2:4" ht="16">
       <c r="D192" s="45" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="193" spans="2:4" ht="16">
       <c r="D193" s="46" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="194" spans="2:4" ht="16">
       <c r="D194" s="46" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="195" spans="2:4" ht="16">
       <c r="D195" s="46" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="196" spans="2:4" ht="16">
       <c r="D196" s="46" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="197" spans="2:4" ht="16">
       <c r="D197" s="46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="199" spans="2:4" ht="16">
@@ -8664,55 +8920,55 @@
         <v>35</v>
       </c>
       <c r="C199" s="36" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D199" s="47" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="200" spans="2:4" ht="16">
       <c r="D200" s="47" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="201" spans="2:4" ht="16">
       <c r="D201" s="47" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="202" spans="2:4" ht="16">
       <c r="D202" s="47" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="203" spans="2:4" ht="16">
       <c r="D203" s="47" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="204" spans="2:4" ht="16">
       <c r="D204" s="48" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="205" spans="2:4" ht="16">
       <c r="D205" s="49" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="206" spans="2:4" ht="16">
       <c r="D206" s="49" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="207" spans="2:4" ht="16">
       <c r="D207" s="49" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="208" spans="2:4" ht="16">
       <c r="D208" s="49" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="210" spans="2:4" ht="16">
@@ -8720,10 +8976,10 @@
         <v>36</v>
       </c>
       <c r="C210" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D210" s="50" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="212" spans="2:4" ht="16">
@@ -8731,30 +8987,30 @@
         <v>37</v>
       </c>
       <c r="C212" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D212" s="48" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="213" spans="2:4" ht="16">
       <c r="D213" s="48" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="214" spans="2:4" ht="16">
       <c r="D214" s="48" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="215" spans="2:4" ht="16">
       <c r="D215" s="48" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="216" spans="2:4" ht="16">
       <c r="D216" s="48" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="219" spans="2:4">
@@ -8762,10 +9018,10 @@
         <v>38</v>
       </c>
       <c r="C219" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D219" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="221" spans="2:4" ht="16">
@@ -8773,35 +9029,35 @@
         <v>39</v>
       </c>
       <c r="C221" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D221" s="50" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="222" spans="2:4" ht="16">
       <c r="D222" s="50" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="223" spans="2:4" ht="16">
       <c r="D223" s="47" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="224" spans="2:4" ht="16">
       <c r="D224" s="47" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="225" spans="2:4" ht="16">
       <c r="D225" s="47" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="226" spans="2:4" ht="16">
       <c r="D226" s="47" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="228" spans="2:4" ht="16">
@@ -8809,66 +9065,66 @@
         <v>40</v>
       </c>
       <c r="C228" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D228" s="47" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="230" spans="2:4" ht="16">
       <c r="C230" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D230" s="45" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="231" spans="2:4" ht="16">
       <c r="D231" s="46" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="232" spans="2:4" ht="16">
       <c r="D232" s="45" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="233" spans="2:4" ht="16">
       <c r="D233" s="46" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="234" spans="2:4" ht="16">
       <c r="D234" s="45" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="235" spans="2:4" ht="16">
       <c r="D235" s="46" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="236" spans="2:4" ht="16">
       <c r="D236" s="45" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="237" spans="2:4" ht="16">
       <c r="D237" s="45" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="239" spans="2:4" ht="16">
       <c r="C239" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="240" spans="2:4" ht="16">
       <c r="D240" s="50" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="242" spans="2:4" ht="16">
@@ -8876,25 +9132,25 @@
         <v>41</v>
       </c>
       <c r="C242" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D242" s="51" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="243" spans="2:4" ht="16">
       <c r="D243" s="51" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="244" spans="2:4" ht="16">
       <c r="D244" s="51" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="245" spans="2:4" ht="16">
       <c r="D245" s="51" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="247" spans="2:4">
@@ -8902,20 +9158,20 @@
         <v>42</v>
       </c>
       <c r="C247" t="s">
+        <v>593</v>
+      </c>
+      <c r="D247" s="51" t="s">
         <v>595</v>
-      </c>
-      <c r="D247" s="51" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="248" spans="2:4">
       <c r="D248" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="249" spans="2:4">
       <c r="D249" s="51" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="251" spans="2:4">
@@ -8923,40 +9179,40 @@
         <v>43</v>
       </c>
       <c r="C251" s="36" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D251" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="252" spans="2:4">
       <c r="D252" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="254" spans="2:4">
       <c r="D254" s="36" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="256" spans="2:4">
       <c r="D256" s="36" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="257" spans="2:4">
       <c r="D257" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="258" spans="2:4">
       <c r="D258" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="259" spans="2:4">
       <c r="D259" s="39" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="261" spans="2:4">
@@ -8964,15 +9220,15 @@
         <v>44</v>
       </c>
       <c r="C261" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D261" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="262" spans="2:4">
       <c r="D262" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="263" spans="2:4">
@@ -8983,15 +9239,15 @@
         <v>45</v>
       </c>
       <c r="C264" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D264" s="52" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="265" spans="2:4">
       <c r="D265" s="52" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="266" spans="2:4">
@@ -9002,10 +9258,10 @@
         <v>46</v>
       </c>
       <c r="C267" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D267" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="269" spans="2:4">
@@ -9013,20 +9269,20 @@
         <v>47</v>
       </c>
       <c r="C269" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D269" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="270" spans="2:4">
       <c r="D270" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="271" spans="2:4">
       <c r="D271" s="39" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="272" spans="2:4">
@@ -9034,10 +9290,10 @@
     </row>
     <row r="273" spans="3:4">
       <c r="C273" s="54" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D273" s="53" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="274" spans="3:4">
@@ -9045,86 +9301,86 @@
     </row>
     <row r="275" spans="3:4">
       <c r="D275" s="57" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="276" spans="3:4">
       <c r="D276" s="57" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="277" spans="3:4">
       <c r="D277" s="57" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="279" spans="3:4">
       <c r="C279" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D279" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="280" spans="3:4">
       <c r="D280" s="57" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="281" spans="3:4">
       <c r="D281" s="57" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="282" spans="3:4">
       <c r="D282" s="57" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="283" spans="3:4">
       <c r="D283" s="57" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="284" spans="3:4">
       <c r="D284" s="57" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="286" spans="3:4" ht="29">
       <c r="C286" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D286" s="35" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="288" spans="3:4">
       <c r="D288" s="57" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="289" spans="2:4">
       <c r="D289" s="57" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="290" spans="2:4">
       <c r="D290" s="57" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="292" spans="2:4">
       <c r="C292" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D292" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="293" spans="2:4">
       <c r="D293" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="295" spans="2:4">
@@ -9132,35 +9388,35 @@
         <v>48</v>
       </c>
       <c r="C295" s="55" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D295" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="296" spans="2:4">
       <c r="D296" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="297" spans="2:4">
       <c r="D297" s="56" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="298" spans="2:4">
       <c r="D298" s="56" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="299" spans="2:4">
       <c r="D299" s="56" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="300" spans="2:4">
       <c r="D300" s="56" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="301" spans="2:4">
@@ -9168,10 +9424,10 @@
     </row>
     <row r="302" spans="2:4">
       <c r="C302" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D302" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="303" spans="2:4">
@@ -9179,131 +9435,131 @@
     </row>
     <row r="304" spans="2:4">
       <c r="D304" s="57" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="305" spans="3:4">
       <c r="D305" s="57" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="306" spans="3:4">
       <c r="D306" s="57" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="308" spans="3:4">
       <c r="C308" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D308" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="310" spans="3:4">
       <c r="D310" s="57" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="311" spans="3:4">
       <c r="D311" s="57" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="312" spans="3:4">
       <c r="D312" s="57" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="314" spans="3:4">
       <c r="C314" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D314" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="315" spans="3:4">
       <c r="D315" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="317" spans="3:4">
       <c r="D317" s="57" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="318" spans="3:4">
       <c r="D318" s="57" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="319" spans="3:4">
       <c r="D319" s="57" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="321" spans="2:4" ht="29">
       <c r="C321" s="35" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D321" s="35" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="323" spans="2:4">
       <c r="D323" s="57" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="324" spans="2:4">
       <c r="D324" s="57" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="325" spans="2:4">
       <c r="D325" s="57" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="328" spans="2:4">
       <c r="C328" s="58" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D328" s="58" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="329" spans="2:4">
       <c r="C329" s="59" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D329" s="60" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="330" spans="2:4">
       <c r="C330" s="59" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D330" s="60" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="331" spans="2:4">
       <c r="C331" s="59" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D331" s="60" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="332" spans="2:4">
       <c r="C332" s="59" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D332" s="60" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="334" spans="2:4">
@@ -9311,25 +9567,25 @@
         <v>49</v>
       </c>
       <c r="C334" s="55" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D334" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="335" spans="2:4">
       <c r="D335" s="39" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="336" spans="2:4">
       <c r="D336" s="39" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="337" spans="2:4">
       <c r="D337" s="39" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="339" spans="2:4">
@@ -9337,101 +9593,101 @@
         <v>50</v>
       </c>
       <c r="C339" s="36" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D339" s="39" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="340" spans="2:4">
       <c r="C340" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="341" spans="2:4">
       <c r="C341" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D341" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="342" spans="2:4">
       <c r="C342" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D342" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="343" spans="2:4">
       <c r="C343" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D343" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="344" spans="2:4">
       <c r="C344" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D344" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="345" spans="2:4">
       <c r="C345" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D345" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="347" spans="2:4">
       <c r="C347" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D347" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="348" spans="2:4">
       <c r="D348" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="350" spans="2:4">
       <c r="D350" s="57" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="352" spans="2:4">
       <c r="C352" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D352" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="354" spans="2:4">
       <c r="D354" s="57" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="355" spans="2:4">
       <c r="D355" s="57" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="356" spans="2:4">
       <c r="D356" s="57" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="357" spans="2:4">
       <c r="D357" s="57" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="359" spans="2:4" ht="48">
@@ -9439,10 +9695,10 @@
         <v>60</v>
       </c>
       <c r="C359" s="61" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D359" s="63" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="363" spans="2:4">
@@ -9450,18 +9706,18 @@
         <v>61</v>
       </c>
       <c r="D363" s="55" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="365" spans="2:4">
       <c r="B365" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C365" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D365" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="366" spans="2:4" ht="16">
@@ -9469,10 +9725,10 @@
         <v>1000</v>
       </c>
       <c r="C366" s="62" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D366" s="62" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="367" spans="2:4" ht="16">
@@ -9480,10 +9736,10 @@
         <v>100</v>
       </c>
       <c r="C367" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D367" s="62" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="368" spans="2:4" ht="16">
@@ -9491,10 +9747,10 @@
         <v>10</v>
       </c>
       <c r="C368" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D368" s="62" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="369" spans="2:4" ht="16">
@@ -9502,10 +9758,10 @@
         <v>1</v>
       </c>
       <c r="C369" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D369" s="62" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="370" spans="2:4" ht="16">
@@ -9513,10 +9769,10 @@
         <v>1</v>
       </c>
       <c r="C370" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D370" s="62" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="371" spans="2:4" ht="16">
@@ -9524,7 +9780,7 @@
     </row>
     <row r="372" spans="2:4" ht="16">
       <c r="D372" s="64" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="374" spans="2:4">
@@ -9532,10 +9788,10 @@
         <v>62</v>
       </c>
       <c r="C374" t="s">
+        <v>701</v>
+      </c>
+      <c r="D374" t="s">
         <v>703</v>
-      </c>
-      <c r="D374" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="376" spans="2:4">
@@ -9543,10 +9799,10 @@
         <v>63</v>
       </c>
       <c r="C376" s="41" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D376" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="378" spans="2:4" ht="29">
@@ -9554,10 +9810,10 @@
         <v>64</v>
       </c>
       <c r="C378" s="41" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D378" s="35" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="380" spans="2:4" ht="16">
@@ -9565,90 +9821,90 @@
         <v>65</v>
       </c>
       <c r="C380" s="62" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D380" s="65" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="381" spans="2:4" ht="16">
       <c r="D381" s="65" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="382" spans="2:4" ht="16">
       <c r="D382" s="65" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="383" spans="2:4" ht="16">
       <c r="D383" s="65" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="384" spans="2:4" ht="16">
       <c r="D384" s="65" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="385" spans="2:4" ht="16">
       <c r="D385" s="65" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="386" spans="2:4" ht="16">
       <c r="D386" s="65" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="387" spans="2:4" ht="16">
       <c r="D387" s="65" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="388" spans="2:4" ht="16">
       <c r="D388" s="65" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="389" spans="2:4" ht="16">
       <c r="D389" s="65" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="390" spans="2:4" ht="16">
       <c r="D390" s="65" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="391" spans="2:4" ht="16">
       <c r="D391" s="65" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="392" spans="2:4" ht="16">
       <c r="D392" s="65" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="393" spans="2:4" ht="16">
       <c r="D393" s="65" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="394" spans="2:4" ht="16">
       <c r="D394" s="65" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="395" spans="2:4" ht="16">
       <c r="D395" s="65" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="396" spans="2:4" ht="16">
       <c r="D396" s="65" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="398" spans="2:4" ht="16">
@@ -9656,75 +9912,75 @@
         <v>66</v>
       </c>
       <c r="C398" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D398" s="66" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="399" spans="2:4" ht="16">
       <c r="D399" s="66" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="400" spans="2:4" ht="16">
       <c r="D400" s="66" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="401" spans="2:4" ht="16">
       <c r="D401" s="66" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="402" spans="2:4" ht="16">
       <c r="D402" s="66" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="403" spans="2:4" ht="16">
       <c r="D403" s="66" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="404" spans="2:4" ht="16">
       <c r="D404" s="66" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="405" spans="2:4" ht="16">
       <c r="D405" s="66" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="406" spans="2:4" ht="16">
       <c r="D406" s="66" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="407" spans="2:4" ht="16">
       <c r="D407" s="66" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="408" spans="2:4" ht="16">
       <c r="D408" s="66" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="409" spans="2:4" ht="16">
       <c r="D409" s="66" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="410" spans="2:4" ht="16">
       <c r="D410" s="66" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="411" spans="2:4" ht="16">
       <c r="D411" s="66" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="413" spans="2:4" ht="16">
@@ -9732,10 +9988,10 @@
         <v>67</v>
       </c>
       <c r="C413" s="66" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D413" s="66" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="415" spans="2:4" ht="16">
@@ -9743,281 +9999,281 @@
         <v>68</v>
       </c>
       <c r="C415" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D415" s="62" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="416" spans="2:4" ht="16">
       <c r="D416" s="62" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="417" spans="3:4" ht="16">
       <c r="D417" s="62" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="418" spans="3:4" ht="16">
       <c r="D418" s="62" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="419" spans="3:4" ht="16">
       <c r="D419" s="62" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="420" spans="3:4" ht="16">
       <c r="D420" s="62" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="421" spans="3:4" ht="16">
       <c r="D421" s="62" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="423" spans="3:4" ht="16">
       <c r="C423" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D423" s="62" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="424" spans="3:4" ht="16">
       <c r="D424" s="62" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="425" spans="3:4" ht="16">
       <c r="D425" s="62" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="426" spans="3:4" ht="16">
       <c r="D426" s="62" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="427" spans="3:4" ht="16">
       <c r="D427" s="62" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="429" spans="3:4" ht="16">
       <c r="D429" s="67" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="430" spans="3:4" ht="16">
       <c r="D430" s="67" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="431" spans="3:4" ht="16">
       <c r="D431" s="67" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="432" spans="3:4">
       <c r="D432" s="68" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="434" spans="3:4" ht="16">
       <c r="C434" t="s">
+        <v>757</v>
+      </c>
+      <c r="D434" s="62" t="s">
         <v>759</v>
-      </c>
-      <c r="D434" s="62" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="435" spans="3:4" ht="16">
       <c r="D435" s="62" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="436" spans="3:4" ht="16">
       <c r="D436" s="62" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="438" spans="3:4" ht="24.5">
       <c r="D438" s="69" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="440" spans="3:4" ht="16">
       <c r="C440" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D440" s="62" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="441" spans="3:4" ht="16">
       <c r="D441" s="62" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="442" spans="3:4" ht="16">
       <c r="D442" s="62" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="443" spans="3:4" ht="16">
       <c r="D443" s="62" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="445" spans="3:4" ht="26.5">
       <c r="D445" s="70" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="447" spans="3:4" ht="16">
       <c r="C447" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D447" s="62" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="448" spans="3:4" ht="16">
       <c r="D448" s="62" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="449" spans="3:4" ht="16">
       <c r="D449" s="62" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="451" spans="3:4" ht="26.5">
       <c r="D451" s="71" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="453" spans="3:4" ht="16">
       <c r="C453" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D453" s="72" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="454" spans="3:4" ht="16">
       <c r="D454" s="72" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="455" spans="3:4" ht="16">
       <c r="D455" s="72" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="457" spans="3:4" ht="39.5">
       <c r="D457" s="70" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="459" spans="3:4">
       <c r="D459" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="460" spans="3:4">
       <c r="D460" s="73" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="461" spans="3:4">
       <c r="D461" s="73" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="462" spans="3:4">
       <c r="D462" s="73" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="463" spans="3:4">
       <c r="D463" s="73" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="464" spans="3:4">
       <c r="D464" s="73" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="467" spans="2:4" ht="20.5" customHeight="1">
       <c r="B467" s="74" t="s">
+        <v>784</v>
+      </c>
+      <c r="C467" s="74" t="s">
+        <v>785</v>
+      </c>
+      <c r="D467" s="74" t="s">
         <v>786</v>
-      </c>
-      <c r="C467" s="74" t="s">
-        <v>787</v>
-      </c>
-      <c r="D467" s="74" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="468" spans="2:4">
       <c r="B468" s="76" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C468" s="75" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D468" s="75" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="469" spans="2:4">
       <c r="B469" s="76" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C469" s="75" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D469" s="75" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="470" spans="2:4" ht="29">
       <c r="B470" s="76" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C470" s="75" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D470" s="75" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="471" spans="2:4">
       <c r="B471" s="76" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C471" s="75" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D471" s="75" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="472" spans="2:4" ht="29">
       <c r="B472" s="76" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C472" s="75" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D472" s="75" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="476" spans="2:4" ht="16">
@@ -10025,45 +10281,45 @@
         <v>69</v>
       </c>
       <c r="C476" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D476" s="77" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="477" spans="2:4">
       <c r="D477" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="478" spans="2:4">
       <c r="D478" s="57" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="479" spans="2:4">
       <c r="D479" s="57" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="480" spans="2:4">
       <c r="D480" s="57" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="481" spans="2:4">
       <c r="D481" s="57" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="482" spans="2:4">
       <c r="D482" s="57" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="483" spans="2:4">
       <c r="D483" s="57" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="485" spans="2:4" ht="16">
@@ -10071,20 +10327,20 @@
         <v>70</v>
       </c>
       <c r="C485" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D485" s="77" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="486" spans="2:4" ht="16">
       <c r="D486" s="77" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="487" spans="2:4">
       <c r="D487" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="489" spans="2:4" ht="16">
@@ -10092,15 +10348,15 @@
         <v>71</v>
       </c>
       <c r="C489" s="78" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D489" s="79" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="490" spans="2:4">
       <c r="D490" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="492" spans="2:4">
@@ -10108,158 +10364,158 @@
         <v>72</v>
       </c>
       <c r="C492" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="D492" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="493" spans="2:4" ht="16">
       <c r="B493" s="80"/>
       <c r="C493" s="82" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D493" s="83" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="494" spans="2:4" ht="16">
       <c r="B494" s="81"/>
       <c r="C494" s="82" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D494" s="83" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="495" spans="2:4" ht="16">
       <c r="B495" s="81"/>
       <c r="C495" s="82" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D495" s="83" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="496" spans="2:4" ht="16">
       <c r="B496" s="81"/>
       <c r="C496" s="82" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D496" s="83" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="497" spans="2:4" ht="16">
       <c r="B497" s="81"/>
       <c r="C497" s="82" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D497" s="83" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="498" spans="2:4" ht="16">
       <c r="B498" s="81"/>
       <c r="C498" s="82" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D498" s="83" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="501" spans="2:4">
       <c r="D501" s="80" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="503" spans="2:4">
       <c r="C503" s="84" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D503" s="85" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="504" spans="2:4">
       <c r="B504" s="81"/>
       <c r="C504" s="84" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="D504" s="85" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="505" spans="2:4">
       <c r="B505" s="81"/>
       <c r="C505" s="84" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D505" s="85" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="506" spans="2:4">
       <c r="B506" s="81"/>
       <c r="C506" s="84" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="D506" s="85" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="507" spans="2:4">
       <c r="B507" s="81"/>
       <c r="C507" s="84" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D507" s="85" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="508" spans="2:4">
       <c r="B508" s="81"/>
       <c r="C508" s="84" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="D508" s="85" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="509" spans="2:4">
       <c r="B509" s="81"/>
       <c r="C509" s="84" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="D509" s="85" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="510" spans="2:4">
       <c r="B510" s="81"/>
       <c r="C510" s="84" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="D510" s="85" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="511" spans="2:4">
       <c r="B511" s="81"/>
       <c r="C511" s="84" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D511" s="85" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="512" spans="2:4">
       <c r="B512" s="81"/>
       <c r="C512" s="84" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D512" s="85" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="515" spans="2:4">
@@ -10267,31 +10523,31 @@
         <v>73</v>
       </c>
       <c r="C515" s="86" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="516" spans="2:4">
       <c r="C516" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D516" s="38" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="517" spans="2:4">
       <c r="C517" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D517" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="518" spans="2:4">
       <c r="C518" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D518" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="521" spans="2:4">
@@ -10299,15 +10555,15 @@
         <v>74</v>
       </c>
       <c r="C521" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D521" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="523" spans="2:4">
       <c r="D523" s="87" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="524" spans="2:4">
@@ -10317,32 +10573,32 @@
     </row>
     <row r="525" spans="2:4">
       <c r="D525" s="87" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="526" spans="2:4">
       <c r="D526" s="87" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="527" spans="2:4">
       <c r="D527" s="87" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="528" spans="2:4">
       <c r="D528" s="87" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="529" spans="4:4">
       <c r="D529" s="87" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="530" spans="4:4">
       <c r="D530" s="87" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="531" spans="4:4">
@@ -10350,57 +10606,57 @@
     </row>
     <row r="532" spans="4:4">
       <c r="D532" s="87" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="533" spans="4:4">
       <c r="D533" s="87" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="534" spans="4:4">
       <c r="D534" s="87" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="535" spans="4:4">
       <c r="D535" s="87" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="536" spans="4:4">
       <c r="D536" s="87" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="537" spans="4:4">
       <c r="D537" s="87" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="538" spans="4:4">
       <c r="D538" s="87" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="539" spans="4:4">
       <c r="D539" s="87" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="540" spans="4:4">
       <c r="D540" s="87" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="541" spans="4:4">
       <c r="D541" s="87" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="542" spans="4:4">
       <c r="D542" s="87" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="543" spans="4:4">
@@ -10408,57 +10664,57 @@
     </row>
     <row r="544" spans="4:4">
       <c r="D544" s="87" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="545" spans="2:4">
       <c r="D545" s="87" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="546" spans="2:4">
       <c r="D546" s="87" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="547" spans="2:4">
       <c r="D547" s="87" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="548" spans="2:4">
       <c r="D548" s="87" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="549" spans="2:4">
       <c r="D549" s="87" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="550" spans="2:4">
       <c r="D550" s="87" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="551" spans="2:4">
       <c r="D551" s="87" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="552" spans="2:4">
       <c r="D552" s="87" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="553" spans="2:4">
       <c r="D553" s="87" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="554" spans="2:4">
       <c r="D554" s="87" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="556" spans="2:4">
@@ -10466,10 +10722,10 @@
         <v>75</v>
       </c>
       <c r="C556" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D556" s="89" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="557" spans="2:4">
@@ -10477,7 +10733,7 @@
     </row>
     <row r="558" spans="2:4">
       <c r="D558" s="91" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="559" spans="2:4">
@@ -10492,47 +10748,47 @@
     </row>
     <row r="561" spans="4:4">
       <c r="D561" s="91" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="562" spans="4:4">
       <c r="D562" s="91" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="563" spans="4:4">
       <c r="D563" s="91" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="564" spans="4:4">
       <c r="D564" s="91" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="565" spans="4:4">
       <c r="D565" s="91" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="566" spans="4:4">
       <c r="D566" s="91" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="567" spans="4:4">
       <c r="D567" s="91" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="568" spans="4:4">
       <c r="D568" s="91" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="569" spans="4:4">
       <c r="D569" s="91" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="570" spans="4:4">
@@ -10540,22 +10796,22 @@
     </row>
     <row r="571" spans="4:4">
       <c r="D571" s="91" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="572" spans="4:4">
       <c r="D572" s="91" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="573" spans="4:4">
       <c r="D573" s="91" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="574" spans="4:4">
       <c r="D574" s="91" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="575" spans="4:4">
@@ -10563,42 +10819,42 @@
     </row>
     <row r="576" spans="4:4">
       <c r="D576" s="91" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="577" spans="4:4">
       <c r="D577" s="91" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="578" spans="4:4">
       <c r="D578" s="91" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="579" spans="4:4">
       <c r="D579" s="91" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="580" spans="4:4">
       <c r="D580" s="91" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="581" spans="4:4">
       <c r="D581" s="91" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="582" spans="4:4">
       <c r="D582" s="91" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="583" spans="4:4">
       <c r="D583" s="91" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="584" spans="4:4">
@@ -10606,32 +10862,32 @@
     </row>
     <row r="585" spans="4:4">
       <c r="D585" s="91" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="586" spans="4:4">
       <c r="D586" s="91" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="587" spans="4:4">
       <c r="D587" s="91" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="588" spans="4:4">
       <c r="D588" s="91" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="589" spans="4:4">
       <c r="D589" s="91" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="590" spans="4:4">
       <c r="D590" s="91" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="591" spans="4:4">
@@ -10639,7 +10895,7 @@
     </row>
     <row r="592" spans="4:4">
       <c r="D592" s="91" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="593" spans="4:4">
@@ -10647,17 +10903,17 @@
     </row>
     <row r="594" spans="4:4">
       <c r="D594" s="91" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="595" spans="4:4">
       <c r="D595" s="91" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="596" spans="4:4">
       <c r="D596" s="91" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="597" spans="4:4">
@@ -10665,27 +10921,27 @@
     </row>
     <row r="598" spans="4:4">
       <c r="D598" s="91" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="599" spans="4:4">
       <c r="D599" s="91" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="600" spans="4:4">
       <c r="D600" s="91" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="601" spans="4:4">
       <c r="D601" s="91" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="602" spans="4:4">
       <c r="D602" s="91" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="603" spans="4:4">
@@ -10695,67 +10951,67 @@
     </row>
     <row r="604" spans="4:4">
       <c r="D604" s="91" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="605" spans="4:4">
       <c r="D605" s="91" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="606" spans="4:4">
       <c r="D606" s="91" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="607" spans="4:4">
       <c r="D607" s="91" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="608" spans="4:4">
       <c r="D608" s="91" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="609" spans="2:4">
       <c r="D609" s="91" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="610" spans="2:4">
       <c r="D610" s="91" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="611" spans="2:4">
       <c r="D611" s="91" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="612" spans="2:4">
       <c r="D612" s="91" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="613" spans="2:4">
       <c r="D613" s="91" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="614" spans="2:4">
       <c r="D614" s="91" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="615" spans="2:4">
       <c r="D615" s="91" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="616" spans="2:4">
       <c r="D616" s="91" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="620" spans="2:4" ht="16">
@@ -10763,10 +11019,10 @@
         <v>76</v>
       </c>
       <c r="C620" s="79" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D620" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="621" spans="2:4" ht="16">
@@ -10774,7 +11030,7 @@
         <v>77</v>
       </c>
       <c r="C621" s="92" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="622" spans="2:4">
@@ -10782,74 +11038,74 @@
         <v>78</v>
       </c>
       <c r="C622" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="D622" s="93" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="624" spans="2:4" ht="16">
       <c r="C624" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="D624" s="79" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="625" spans="2:4" ht="16">
       <c r="C625" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="D625" s="79" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="626" spans="2:4" ht="16">
       <c r="C626" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="D626" s="79" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="627" spans="2:4" ht="16">
       <c r="C627" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="D627" s="79" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="628" spans="2:4" ht="16">
       <c r="C628" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D628" s="79" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="629" spans="2:4" ht="16">
       <c r="C629" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D629" s="79" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="630" spans="2:4" ht="16">
       <c r="C630" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D630" s="79" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="631" spans="2:4" ht="16">
       <c r="C631" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="D631" s="79" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="633" spans="2:4">
@@ -10857,10 +11113,10 @@
         <v>79</v>
       </c>
       <c r="C633" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D633" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="635" spans="2:4">
@@ -10868,25 +11124,25 @@
         <v>80</v>
       </c>
       <c r="C635" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="D635" s="57" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="636" spans="2:4">
       <c r="D636" s="57" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="637" spans="2:4">
       <c r="D637" s="57" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="638" spans="2:4">
       <c r="D638" s="57" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="639" spans="2:4">
@@ -10894,22 +11150,22 @@
     </row>
     <row r="640" spans="2:4">
       <c r="D640" s="57" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="641" spans="4:4">
       <c r="D641" s="57" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="642" spans="4:4">
       <c r="D642" s="57" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="643" spans="4:4">
       <c r="D643" s="57" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="644" spans="4:4">
@@ -10917,22 +11173,22 @@
     </row>
     <row r="645" spans="4:4">
       <c r="D645" s="57" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="646" spans="4:4">
       <c r="D646" s="57" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="647" spans="4:4">
       <c r="D647" s="57" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="648" spans="4:4">
       <c r="D648" s="57" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="649" spans="4:4">
@@ -10940,72 +11196,72 @@
     </row>
     <row r="650" spans="4:4">
       <c r="D650" s="57" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="651" spans="4:4">
       <c r="D651" s="57" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="652" spans="4:4">
       <c r="D652" s="57" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="653" spans="4:4">
       <c r="D653" s="57" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="654" spans="4:4">
       <c r="D654" s="57" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="655" spans="4:4">
       <c r="D655" s="57" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="656" spans="4:4">
       <c r="D656" s="57" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="657" spans="2:4">
       <c r="D657" s="57" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="658" spans="2:4">
       <c r="D658" s="57" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="659" spans="2:4">
       <c r="D659" s="57" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="660" spans="2:4">
       <c r="D660" s="57" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="661" spans="2:4">
       <c r="D661" s="57" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="662" spans="2:4">
       <c r="D662" s="57" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="663" spans="2:4">
       <c r="D663" s="57" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="665" spans="2:4">
@@ -11013,15 +11269,15 @@
         <v>90</v>
       </c>
       <c r="C665" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="D665" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="667" spans="2:4">
       <c r="D667" s="94" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="668" spans="2:4">
@@ -11029,7 +11285,7 @@
     </row>
     <row r="669" spans="2:4">
       <c r="D669" s="94" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="671" spans="2:4">
@@ -11037,12 +11293,12 @@
         <v>91</v>
       </c>
       <c r="C671" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="672" spans="2:4">
       <c r="D672" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="673" spans="3:4">
@@ -11050,56 +11306,56 @@
     </row>
     <row r="674" spans="3:4">
       <c r="C674" s="97" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="D674" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="675" spans="3:4">
       <c r="C675" s="97" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="D675" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="676" spans="3:4">
       <c r="C676" s="97" t="s">
+        <v>973</v>
+      </c>
+      <c r="D676" t="s">
         <v>975</v>
-      </c>
-      <c r="D676" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="677" spans="3:4">
       <c r="C677" s="97" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="D677" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="678" spans="3:4">
       <c r="C678" s="97" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="D678" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="679" spans="3:4">
       <c r="C679" s="97" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="D679" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="681" spans="3:4">
       <c r="C681" s="95"/>
       <c r="D681" s="97" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="682" spans="3:4">
@@ -11108,48 +11364,48 @@
     </row>
     <row r="683" spans="3:4">
       <c r="C683" s="97" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="D683" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="684" spans="3:4">
       <c r="C684" s="97" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="D684" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="685" spans="3:4">
       <c r="C685" s="97" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="D685" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="686" spans="3:4">
       <c r="C686" s="97" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="D686" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="687" spans="3:4">
       <c r="C687" s="97" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="D687" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="688" spans="3:4">
       <c r="C688" s="5"/>
       <c r="D688" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="689" spans="2:4">
@@ -11160,87 +11416,249 @@
         <v>92</v>
       </c>
       <c r="C690" s="98" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="692" spans="2:4">
       <c r="C692" s="97" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="D692" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="693" spans="2:4">
       <c r="C693" s="97" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D693" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="694" spans="2:4">
       <c r="C694" s="97" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D694" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="695" spans="2:4">
       <c r="C695" s="97" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D695" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="696" spans="2:4">
       <c r="C696" s="97" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D696" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="697" spans="2:4">
       <c r="C697" s="97" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D697" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="698" spans="2:4">
       <c r="C698" s="97" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D698" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="699" spans="2:4">
       <c r="C699" s="97" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="D699" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="700" spans="2:4">
       <c r="C700" s="97" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="D700" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="701" spans="2:4">
       <c r="C701" s="97" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D701" t="s">
-        <v>1010</v>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="703" spans="2:4">
+      <c r="B703">
+        <v>93</v>
+      </c>
+      <c r="C703" s="97" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="704" spans="2:4">
+      <c r="B704">
+        <v>94</v>
+      </c>
+      <c r="C704" s="97" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D704" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="705" spans="2:4">
+      <c r="D705" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="706" spans="2:4">
+      <c r="D706" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="708" spans="2:4">
+      <c r="C708" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D708" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="709" spans="2:4">
+      <c r="D709" s="39" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="710" spans="2:4">
+      <c r="D710" s="39" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="711" spans="2:4">
+      <c r="D711" s="39" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="712" spans="2:4">
+      <c r="D712" s="39" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="713" spans="2:4">
+      <c r="D713" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="714" spans="2:4">
+      <c r="D714" s="39" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="715" spans="2:4">
+      <c r="D715" s="39" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="716" spans="2:4">
+      <c r="D716" s="39"/>
+    </row>
+    <row r="717" spans="2:4">
+      <c r="B717">
+        <v>95</v>
+      </c>
+      <c r="C717" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D717" s="41" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="718" spans="2:4">
+      <c r="D718" s="41" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="719" spans="2:4">
+      <c r="D719" s="41" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="720" spans="2:4">
+      <c r="D720" s="41" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="721" spans="2:4">
+      <c r="D721" s="41" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="722" spans="2:4">
+      <c r="D722" s="41" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="723" spans="2:4">
+      <c r="D723" s="41" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="724" spans="2:4">
+      <c r="D724" s="41" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="726" spans="2:4">
+      <c r="B726">
+        <v>96</v>
+      </c>
+      <c r="C726" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D726" s="41" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="727" spans="2:4">
+      <c r="D727" s="41" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="728" spans="2:4">
+      <c r="D728" s="41" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="729" spans="2:4">
+      <c r="D729" s="41" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="730" spans="2:4">
+      <c r="D730" s="41" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="731" spans="2:4">
+      <c r="D731" s="41" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="733" spans="2:4">
+      <c r="B733">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -11263,7 +11681,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="3:5">
@@ -11271,7 +11689,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="3:5">
@@ -11279,7 +11697,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -11287,7 +11705,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -11295,7 +11713,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="3:5">
@@ -11303,7 +11721,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="3:5">
@@ -11311,7 +11729,7 @@
         <v>6</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="3:5">
@@ -11319,7 +11737,7 @@
         <v>7</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="3:5">
@@ -11327,7 +11745,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="3:5">
@@ -11335,7 +11753,7 @@
         <v>9</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="3:5">
@@ -11343,17 +11761,17 @@
         <v>10</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="15.5">
       <c r="B18" s="5"/>
       <c r="C18" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="2:5">
@@ -11437,7 +11855,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -11663,7 +12081,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>43</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="42" spans="2:5">
@@ -11671,19 +12089,19 @@
         <v>22</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="2:5" ht="15.5">
       <c r="B43" s="5"/>
       <c r="C43" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
@@ -11693,13 +12111,13 @@
         <v>23</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="2:5">
@@ -11707,13 +12125,13 @@
         <v>24</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="2:5">
@@ -11721,13 +12139,13 @@
         <v>25</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="2:5">
@@ -11735,13 +12153,13 @@
         <v>26</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="2:5">
@@ -11749,13 +12167,13 @@
         <v>27</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="2:5">
@@ -11763,13 +12181,13 @@
         <v>28</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="2:5">
@@ -11777,13 +12195,13 @@
         <v>29</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="2:5">
@@ -11791,13 +12209,13 @@
         <v>30</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="2:5">
@@ -11805,13 +12223,13 @@
         <v>31</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="2:5">
@@ -11819,13 +12237,13 @@
         <v>32</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" spans="2:5">
@@ -11833,13 +12251,13 @@
         <v>33</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="2:5">
@@ -11847,13 +12265,13 @@
         <v>34</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="2:5">
@@ -11861,13 +12279,13 @@
         <v>35</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="2:5">
@@ -11878,13 +12296,13 @@
         <v>36</v>
       </c>
       <c r="C59" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D59" t="s">
         <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" spans="2:5">
@@ -11892,13 +12310,13 @@
         <v>37</v>
       </c>
       <c r="C60" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D60" t="s">
         <v>1</v>
       </c>
       <c r="E60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="2:5">
@@ -11906,13 +12324,13 @@
         <v>38</v>
       </c>
       <c r="C61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D61" t="s">
         <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="2:5">
@@ -11920,13 +12338,13 @@
         <v>39</v>
       </c>
       <c r="C62" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D62" t="s">
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="2:5">
@@ -11934,13 +12352,13 @@
         <v>40</v>
       </c>
       <c r="C63" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D63" t="s">
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="2:5">
@@ -11951,7 +12369,7 @@
         <v>1</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" spans="2:5">
@@ -11959,13 +12377,13 @@
         <v>42</v>
       </c>
       <c r="C65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D65" t="s">
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="2:5">
@@ -11973,13 +12391,13 @@
         <v>43</v>
       </c>
       <c r="C66" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D66" t="s">
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="2:5">
@@ -11987,13 +12405,13 @@
         <v>44</v>
       </c>
       <c r="C67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D67" t="s">
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="2:5">
@@ -12001,13 +12419,13 @@
         <v>45</v>
       </c>
       <c r="C68" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D68" t="s">
         <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="2:5">
@@ -12015,13 +12433,13 @@
         <v>46</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D69" t="s">
         <v>1</v>
       </c>
       <c r="E69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70" spans="2:5">
@@ -12029,13 +12447,13 @@
         <v>47</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>107</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="71" spans="2:5">
@@ -12043,13 +12461,13 @@
         <v>48</v>
       </c>
       <c r="C71" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D71" t="s">
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72" spans="2:5">
@@ -12057,13 +12475,13 @@
         <v>49</v>
       </c>
       <c r="C72" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D72" t="s">
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="73" spans="2:5">
@@ -12071,13 +12489,13 @@
         <v>50</v>
       </c>
       <c r="C73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D73" t="s">
         <v>1</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="74" spans="2:5">
@@ -12085,13 +12503,13 @@
         <v>51</v>
       </c>
       <c r="C74" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D74" t="s">
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="75" spans="2:5">
@@ -12099,13 +12517,13 @@
         <v>52</v>
       </c>
       <c r="C75" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D75" t="s">
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="76" spans="2:5">
@@ -12113,13 +12531,13 @@
         <v>53</v>
       </c>
       <c r="C76" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D76" t="s">
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="77" spans="2:5">
@@ -12127,13 +12545,13 @@
         <v>54</v>
       </c>
       <c r="C77" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D77" t="s">
         <v>1</v>
       </c>
       <c r="E77" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="78" spans="2:5">
@@ -12141,13 +12559,13 @@
         <v>55</v>
       </c>
       <c r="C78" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D78" t="s">
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="2:5">
@@ -12155,13 +12573,13 @@
         <v>56</v>
       </c>
       <c r="C79" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D79" t="s">
         <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="80" spans="2:5">
@@ -12169,13 +12587,13 @@
         <v>57</v>
       </c>
       <c r="C80" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D80" t="s">
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="81" spans="2:5">
@@ -12183,13 +12601,13 @@
         <v>58</v>
       </c>
       <c r="C81" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D81" t="s">
         <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="2:5">
@@ -12197,13 +12615,13 @@
         <v>59</v>
       </c>
       <c r="C82" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D82" t="s">
         <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="83" spans="2:5">
@@ -12211,13 +12629,13 @@
         <v>60</v>
       </c>
       <c r="C83" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D83" t="s">
         <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="84" spans="2:5">
@@ -12225,13 +12643,13 @@
         <v>61</v>
       </c>
       <c r="C84" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D84" t="s">
         <v>1</v>
       </c>
       <c r="E84" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="85" spans="2:5">
@@ -12239,13 +12657,13 @@
         <v>62</v>
       </c>
       <c r="C85" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D85" t="s">
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="86" spans="2:5">
@@ -12253,13 +12671,13 @@
         <v>63</v>
       </c>
       <c r="C86" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D86" t="s">
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="87" spans="2:5">
@@ -12267,13 +12685,13 @@
         <v>64</v>
       </c>
       <c r="C87" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D87" t="s">
         <v>1</v>
       </c>
       <c r="E87" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="88" spans="2:5">
@@ -12281,13 +12699,13 @@
         <v>65</v>
       </c>
       <c r="C88" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D88" t="s">
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="89" spans="2:5">
@@ -12295,13 +12713,13 @@
         <v>66</v>
       </c>
       <c r="C89" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D89" t="s">
         <v>1</v>
       </c>
       <c r="E89" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="90" spans="2:5">
@@ -12309,13 +12727,13 @@
         <v>67</v>
       </c>
       <c r="C90" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D90" t="s">
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="91" spans="2:5">
@@ -12323,13 +12741,13 @@
         <v>68</v>
       </c>
       <c r="C91" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D91" t="s">
         <v>1</v>
       </c>
       <c r="E91" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="92" spans="2:5">
@@ -12337,13 +12755,13 @@
         <v>69</v>
       </c>
       <c r="C92" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D92" t="s">
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="93" spans="2:5">
@@ -12351,13 +12769,13 @@
         <v>70</v>
       </c>
       <c r="C93" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D93" t="s">
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="94" spans="2:5">
@@ -12365,13 +12783,13 @@
         <v>71</v>
       </c>
       <c r="C94" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D94" t="s">
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -12399,7 +12817,7 @@
     <row r="8" spans="4:8" ht="15.5">
       <c r="D8" s="27"/>
       <c r="E8" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:8">
@@ -12407,33 +12825,33 @@
         <v>1</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="4:8">
       <c r="D10" s="22" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:8">
       <c r="D11" s="22"/>
       <c r="E11" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G11" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" spans="4:8">
       <c r="D12" s="22"/>
       <c r="E12" s="23" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:8">
@@ -12443,10 +12861,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H13" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" spans="4:8">
@@ -12454,113 +12872,113 @@
         <v>2</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H14" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="4:8">
       <c r="D15" s="22" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H15" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" spans="4:8">
       <c r="D16" s="22"/>
       <c r="E16" s="23" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F16">
         <v>3</v>
       </c>
       <c r="G16" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H16" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="D17" s="22"/>
       <c r="E17" s="23" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F17">
         <v>4</v>
       </c>
       <c r="G17" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H17" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" spans="3:8">
       <c r="D18" s="22"/>
       <c r="E18" s="23" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="3:8">
       <c r="D19" s="24"/>
       <c r="E19" s="25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="3:8">
       <c r="E21" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="22" spans="3:8">
       <c r="E22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23" spans="3:8">
       <c r="E23" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="3:8">
       <c r="E24" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="3:8">
       <c r="D26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E26" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="3:8">
       <c r="D27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="3:8" ht="15.5">
       <c r="D29" s="11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" spans="3:8">
@@ -12568,10 +12986,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E31" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" spans="3:8">
@@ -12579,10 +12997,10 @@
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E32" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" spans="3:5">
@@ -12590,10 +13008,10 @@
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E33" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" spans="3:5">
@@ -12601,10 +13019,10 @@
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E34" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35" spans="3:5">
@@ -12612,10 +13030,10 @@
         <v>5</v>
       </c>
       <c r="D35" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E35" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36" spans="3:5">
@@ -12623,10 +13041,10 @@
         <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E36" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="37" spans="3:5">
@@ -12634,10 +13052,10 @@
         <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38" spans="3:5">
@@ -12645,10 +13063,10 @@
         <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E38" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="39" spans="3:5">
@@ -12656,10 +13074,10 @@
         <v>9</v>
       </c>
       <c r="D39" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E39" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="40" spans="3:5">
@@ -12667,10 +13085,10 @@
         <v>10</v>
       </c>
       <c r="D40" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E40" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="41" spans="3:5">
@@ -12678,10 +13096,10 @@
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E41" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="42" spans="3:5">
@@ -12689,10 +13107,10 @@
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E42" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="43" spans="3:5">
@@ -12700,10 +13118,10 @@
         <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E43" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="44" spans="3:5">
@@ -12711,10 +13129,10 @@
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E44" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="45" spans="3:5">
@@ -12722,10 +13140,10 @@
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E45" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" spans="3:5">
@@ -12733,10 +13151,10 @@
         <v>16</v>
       </c>
       <c r="D46" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E46" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="47" spans="3:5">
@@ -12744,10 +13162,10 @@
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E47" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="48" spans="3:5">
@@ -12755,10 +13173,10 @@
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E48" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="49" spans="3:5">
@@ -12766,10 +13184,10 @@
         <v>19</v>
       </c>
       <c r="D49" t="s">
+        <v>345</v>
+      </c>
+      <c r="E49" t="s">
         <v>347</v>
-      </c>
-      <c r="E49" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="50" spans="3:5">
@@ -12777,10 +13195,10 @@
         <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E50" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="51" spans="3:5">
@@ -12788,10 +13206,10 @@
         <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E51" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="52" spans="3:5">
@@ -12799,10 +13217,10 @@
         <v>22</v>
       </c>
       <c r="D52" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E52" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="53" spans="3:5" ht="19.5" customHeight="1">
@@ -12810,10 +13228,10 @@
         <v>23</v>
       </c>
       <c r="D53" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E53" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="54" spans="3:5" ht="46.5" customHeight="1">
@@ -12821,10 +13239,10 @@
         <v>24</v>
       </c>
       <c r="D54" s="35" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E54" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="55" spans="3:5">
@@ -12832,10 +13250,10 @@
         <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E55" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="56" spans="3:5">
@@ -12843,10 +13261,10 @@
         <v>26</v>
       </c>
       <c r="D56" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E56" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="57" spans="3:5">
@@ -12854,10 +13272,10 @@
         <v>27</v>
       </c>
       <c r="D57" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E57" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="58" spans="3:5">
@@ -12865,10 +13283,10 @@
         <v>28</v>
       </c>
       <c r="D58" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E58" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="59" spans="3:5">
@@ -12876,10 +13294,10 @@
         <v>29</v>
       </c>
       <c r="D59" t="s">
+        <v>365</v>
+      </c>
+      <c r="E59" t="s">
         <v>367</v>
-      </c>
-      <c r="E59" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="60" spans="3:5">
@@ -12887,10 +13305,10 @@
         <v>30</v>
       </c>
       <c r="D60" t="s">
+        <v>366</v>
+      </c>
+      <c r="E60" t="s">
         <v>368</v>
-      </c>
-      <c r="E60" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="61" spans="3:5">
@@ -12898,10 +13316,10 @@
         <v>31</v>
       </c>
       <c r="D61" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E61" s="36" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="62" spans="3:5">
@@ -12909,15 +13327,15 @@
         <v>32</v>
       </c>
       <c r="D62" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E62" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="63" spans="3:5" ht="15.5">
       <c r="D63" s="11" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="64" spans="3:5">
@@ -12925,10 +13343,10 @@
         <v>33</v>
       </c>
       <c r="D64" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E64" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65" spans="3:5">
@@ -12936,10 +13354,10 @@
         <v>34</v>
       </c>
       <c r="D65" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E65" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="66" spans="3:5">
@@ -12947,10 +13365,10 @@
         <v>35</v>
       </c>
       <c r="D66" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E66" s="36" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="67" spans="3:5">
@@ -12958,10 +13376,10 @@
         <v>36</v>
       </c>
       <c r="D67" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E67" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="68" spans="3:5">
@@ -12969,10 +13387,10 @@
         <v>37</v>
       </c>
       <c r="D68" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E68" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="69" spans="3:5">
@@ -12980,10 +13398,10 @@
         <v>38</v>
       </c>
       <c r="D69" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E69" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="70" spans="3:5">
@@ -12991,10 +13409,10 @@
         <v>39</v>
       </c>
       <c r="D70" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E70" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -13015,7 +13433,7 @@
   <sheetData>
     <row r="10" spans="3:7">
       <c r="E10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="11" spans="3:7">
@@ -13024,7 +13442,7 @@
       </c>
       <c r="D11" s="18"/>
       <c r="E11" s="18" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="3:7">
@@ -13033,24 +13451,24 @@
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="18" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="3:7">
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G13" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="3:7">
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="3:7">
@@ -13059,14 +13477,14 @@
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="18" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="3:7">
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
       <c r="E16" s="18" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="3:5">
@@ -13075,30 +13493,30 @@
       </c>
       <c r="D17" s="18"/>
       <c r="E17" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="3:5">
       <c r="C18" s="18"/>
       <c r="D18" s="19" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="3:5">
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
       <c r="E19" s="18" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="3:5">
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
       <c r="E20" s="18" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="3:5">
@@ -13107,132 +13525,132 @@
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="18" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="3:5">
       <c r="C22" s="18"/>
       <c r="D22" s="19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="3:5">
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="3:5">
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
       <c r="E24" s="18" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="3:5">
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
       <c r="E25" s="18" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="3:5">
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
       <c r="E26" s="18" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="3:5">
       <c r="C27" s="18"/>
       <c r="D27" s="19" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="3:5">
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
       <c r="E28" s="18" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="3:5">
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
       <c r="E29" s="18" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="3:5">
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
       <c r="E30" s="18" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="3:5">
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
       <c r="E31" s="18" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="3:5">
       <c r="C32" s="18"/>
       <c r="D32" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>229</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="33" spans="3:5">
       <c r="C33" s="18"/>
       <c r="D33" s="18"/>
       <c r="E33" s="18" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34" spans="3:5">
       <c r="C34" s="18"/>
       <c r="D34" s="18"/>
       <c r="E34" s="18" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" spans="3:5">
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>
       <c r="E35" s="18" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36" spans="3:5">
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
       <c r="E36" s="18" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37" spans="3:5">
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
       <c r="E37" s="18" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="3:5">
       <c r="C38" s="18"/>
       <c r="D38" s="18"/>
       <c r="E38" s="18" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39" spans="3:5" ht="15.5">
@@ -13240,92 +13658,92 @@
         <v>6</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40" spans="3:5">
       <c r="C40" s="18"/>
       <c r="D40" s="18" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="41" spans="3:5">
       <c r="C41" s="18"/>
       <c r="D41" s="18" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42" spans="3:5">
       <c r="C42" s="18"/>
       <c r="D42" s="18" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43" spans="3:5">
       <c r="C43" s="18"/>
       <c r="D43" s="18" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="44" spans="3:5">
       <c r="C44" s="18"/>
       <c r="D44" s="18" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="3:5">
       <c r="D48" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E48" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="49" spans="4:5">
       <c r="E49" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="50" spans="4:5">
       <c r="E50" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="52" spans="4:5">
       <c r="D52" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E52" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="53" spans="4:5">
       <c r="E53" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="56" spans="4:5" ht="18.5">
       <c r="D56" s="30"/>
       <c r="E56" s="30" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="4:5">
@@ -13337,13 +13755,13 @@
         <v>1</v>
       </c>
       <c r="E58" s="31" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="4:5">
       <c r="D59" s="30"/>
       <c r="E59" s="32" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="60" spans="4:5">
@@ -13355,19 +13773,19 @@
         <v>2</v>
       </c>
       <c r="E61" s="33" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="62" spans="4:5">
       <c r="D62" s="30"/>
       <c r="E62" s="30" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63" spans="4:5">
       <c r="D63" s="30"/>
       <c r="E63" s="30" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="64" spans="4:5">
@@ -13379,19 +13797,19 @@
         <v>3</v>
       </c>
       <c r="E65" s="33" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="66" spans="4:5">
       <c r="D66" s="30"/>
       <c r="E66" s="30" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="67" spans="4:5">
       <c r="D67" s="30"/>
       <c r="E67" s="30" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="68" spans="4:5">
@@ -13403,19 +13821,19 @@
         <v>4</v>
       </c>
       <c r="E69" s="33" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="70" spans="4:5">
       <c r="D70" s="30"/>
       <c r="E70" s="30" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="71" spans="4:5">
       <c r="D71" s="30"/>
       <c r="E71" s="30" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="72" spans="4:5">
@@ -13427,19 +13845,19 @@
         <v>5</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="74" spans="4:5">
       <c r="D74" s="30"/>
       <c r="E74" s="30" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="75" spans="4:5">
       <c r="D75" s="30"/>
       <c r="E75" s="30" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="76" spans="4:5">
@@ -13451,13 +13869,13 @@
         <v>6</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="78" spans="4:5">
       <c r="D78" s="30"/>
       <c r="E78" s="30" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="79" spans="4:5">
@@ -13484,7 +13902,7 @@
         <v>1048576</v>
       </c>
       <c r="B1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -13492,17 +13910,17 @@
         <v>16384</v>
       </c>
       <c r="B3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="I6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="I8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/doc/NOTES.xlsx
+++ b/doc/NOTES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MY PC\Documents\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C9C5B2-8A67-49C6-AE6F-EA52AE9FD3BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58E4391-A11F-418F-8836-F764ED230D4E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="1041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="1139">
   <si>
     <t>HTML</t>
   </si>
@@ -6065,9 +6065,6 @@
     <t xml:space="preserve"> Defines a perspective view for a 3D transformed element </t>
   </si>
   <si>
-    <t xml:space="preserve">Supports Multi Selects inside options tag </t>
-  </si>
-  <si>
     <t>Insertion : underline content as inserted rn</t>
   </si>
   <si>
@@ -6325,13 +6322,1234 @@
       </rPr>
       <t xml:space="preserve"> control order of appearance</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Supports Multi Selects with options tag </t>
+  </si>
+  <si>
+    <t>Grid</t>
+  </si>
+  <si>
+    <t>Property</t>
+  </si>
+  <si>
+    <t>Values/Examples</t>
+  </si>
+  <si>
+    <t>display</t>
+  </si>
+  <si>
+    <t>grid-template-columns</t>
+  </si>
+  <si>
+    <t>Defines the number and size of columns.</t>
+  </si>
+  <si>
+    <t>grid-template-rows</t>
+  </si>
+  <si>
+    <t>Defines the number and size of rows.</t>
+  </si>
+  <si>
+    <t>grid-template-areas</t>
+  </si>
+  <si>
+    <t>Defines named areas in the grid layout.</t>
+  </si>
+  <si>
+    <t>grid-column</t>
+  </si>
+  <si>
+    <t>grid-row</t>
+  </si>
+  <si>
+    <t>grid-column-start/end</t>
+  </si>
+  <si>
+    <t>Sets start/end lines for grid items.</t>
+  </si>
+  <si>
+    <t>grid-row-start/end</t>
+  </si>
+  <si>
+    <t>grid-auto-columns</t>
+  </si>
+  <si>
+    <t>Sets size for implicitly created columns.</t>
+  </si>
+  <si>
+    <t>100px</t>
+  </si>
+  <si>
+    <t>grid-auto-rows</t>
+  </si>
+  <si>
+    <t>Sets size for implicitly created rows.</t>
+  </si>
+  <si>
+    <t>minmax(100px, auto)</t>
+  </si>
+  <si>
+    <t>grid-auto-flow</t>
+  </si>
+  <si>
+    <t>Controls direction for auto-placed items.</t>
+  </si>
+  <si>
+    <t>Sets spacing between rows/columns.</t>
+  </si>
+  <si>
+    <t>justify-items</t>
+  </si>
+  <si>
+    <t>Aligns items horizontally inside each cell.</t>
+  </si>
+  <si>
+    <t>align-items</t>
+  </si>
+  <si>
+    <t>Aligns items vertically inside each cell.</t>
+  </si>
+  <si>
+    <t>justify-content</t>
+  </si>
+  <si>
+    <t>Aligns the entire grid horizontally.</t>
+  </si>
+  <si>
+    <t>align-content</t>
+  </si>
+  <si>
+    <t>Aligns the entire grid vertically.</t>
+  </si>
+  <si>
+    <t>place-items</t>
+  </si>
+  <si>
+    <t>center stretch</t>
+  </si>
+  <si>
+    <t>place-content</t>
+  </si>
+  <si>
+    <t>space-between center</t>
+  </si>
+  <si>
+    <t>place-self</t>
+  </si>
+  <si>
+    <t>start end</t>
+  </si>
+  <si>
+    <t>justify-self</t>
+  </si>
+  <si>
+    <t>Overrides horizontal alignment per grid item.</t>
+  </si>
+  <si>
+    <t>align-self</t>
+  </si>
+  <si>
+    <t>Overrides vertical alignment per grid item.</t>
+  </si>
+  <si>
+    <t>The Grid Layout Module offers a grid-based layout system, with rows and columns.</t>
+  </si>
+  <si>
+    <t>The Grid Layout Module allows developers to easily create complex web layouts.</t>
+  </si>
+  <si>
+    <t>The Grid Layout Module makes it easier to design a responsive layout structure, without using float or positioning.</t>
+  </si>
+  <si>
+    <t>The CSS grid properties are supported in all modern browsers.</t>
+  </si>
+  <si>
+    <t> Two-Dimensional Layout</t>
+  </si>
+  <si>
+    <t>A grid always consists of:</t>
+  </si>
+  <si>
+    <t>The CSS Grid Layout should be used for two-dimensional layout, with rows AND columns.</t>
+  </si>
+  <si>
+    <t>The CSS Flexbox Layout should be used for one-dimensional layout, with rows OR columns.</t>
+  </si>
+  <si>
+    <t>Grid Terminology:</t>
+  </si>
+  <si>
+    <r>
+      <t>Grid Container</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: The parent (container) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;div&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> element</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Grid Items</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: The items inside the container </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;div&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Grid Container</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: The parent element where grid is defined (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>display: grid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Grid Item</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: The child elements inside the grid container</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Grid Lines</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: The dividing lines between rows and columns</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Grid Tracks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Rows or columns themselves</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Grid Cell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: The space between two adjacent row and column lines</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Grid Area</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: A rectangular space covering one or more cells</t>
+    </r>
+  </si>
+  <si>
+    <t>Properties</t>
+  </si>
+  <si>
+    <r>
+      <t>grid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>inline-grid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>100px</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>30%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>auto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>1fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>repeat(5, 1fr)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>minmax(50px, 200px)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Same as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>grid-template-columns</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>"header header"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>"sidebar main"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>"footer footer"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Shorthand for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>grid-column-start</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>grid-column-end</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1 / 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>span 2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Shorthand for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>grid-row-start</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>grid-row-end</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>span 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>2 / 4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>span 3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>span 2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>column</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>row dense</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>column dense</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>gap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>row-gap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>column-gap</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10px</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>20px 30px</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>start</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>end</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>center</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>stretch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (default)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Same as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>justify-items</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>start</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>end</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>center</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>space-around</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>space-between</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>space-evenly</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Same as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>justify-content</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Shorthand for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>align-items</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>justify-items</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Shorthand for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>align-content</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>justify-content</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Shorthand for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>align-self</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>justify-self</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>start</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>end</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>center</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>stretch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Same as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF404040"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>justify-self</t>
+    </r>
+  </si>
+  <si>
+    <t>Flexbox VS Grid</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Axis</t>
+  </si>
+  <si>
+    <t>1D</t>
+  </si>
+  <si>
+    <t>2D</t>
+  </si>
+  <si>
+    <t>Best For</t>
+  </si>
+  <si>
+    <t>Components</t>
+  </si>
+  <si>
+    <t>Page layout</t>
+  </si>
+  <si>
+    <t>Nesting</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>Overlap Support</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Learning Curve</t>
+  </si>
+  <si>
+    <t>Easier</t>
+  </si>
+  <si>
+    <t>Slightly Harder</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="48">
+  <fonts count="53">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6655,6 +7873,38 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -6795,7 +8045,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6822,15 +8072,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -6857,53 +8099,23 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6920,17 +8132,12 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -6940,8 +8147,6 @@
     <xf numFmtId="0" fontId="32" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6950,9 +8155,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6979,26 +8181,10 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -7010,6 +8196,130 @@
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7762,27 +9072,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B8:D733"/>
+  <dimension ref="B8:E784"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="29.81640625" customWidth="1"/>
-    <col min="4" max="4" width="121.81640625" customWidth="1"/>
+    <col min="4" max="4" width="63.453125" style="31" customWidth="1"/>
+    <col min="5" max="5" width="26.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="8" spans="3:4" ht="15.5">
-      <c r="D8" s="11"/>
+      <c r="D8" s="77"/>
     </row>
     <row r="9" spans="3:4" ht="18.5">
       <c r="C9" s="4"/>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="78" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="10" spans="3:4">
+    <row r="10" spans="3:4" ht="29">
       <c r="C10" s="4">
         <v>1</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="79" t="s">
         <v>147</v>
       </c>
     </row>
@@ -7790,7 +9101,7 @@
       <c r="C11" s="4">
         <v>2</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="79" t="s">
         <v>152</v>
       </c>
     </row>
@@ -7798,7 +9109,7 @@
       <c r="C12" s="4">
         <v>3</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="79" t="s">
         <v>148</v>
       </c>
     </row>
@@ -7806,7 +9117,7 @@
       <c r="C13" s="4">
         <v>4</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="79" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7814,23 +9125,23 @@
       <c r="C14" s="4">
         <v>5</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="79" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="3:4">
+    <row r="15" spans="3:4" ht="29">
       <c r="C15" s="4">
         <v>6</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="79" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="18.5">
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="80" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7841,7 +9152,7 @@
       <c r="C19" t="s">
         <v>155</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="31" t="s">
         <v>164</v>
       </c>
     </row>
@@ -7852,7 +9163,7 @@
       <c r="C20" t="s">
         <v>156</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="31" t="s">
         <v>403</v>
       </c>
     </row>
@@ -7863,7 +9174,7 @@
       <c r="C21" t="s">
         <v>157</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="31" t="s">
         <v>165</v>
       </c>
     </row>
@@ -7874,7 +9185,7 @@
       <c r="C22" t="s">
         <v>158</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="31" t="s">
         <v>166</v>
       </c>
     </row>
@@ -7885,18 +9196,18 @@
       <c r="C23" t="s">
         <v>159</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="31" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
+    <row r="24" spans="2:4" ht="29">
       <c r="B24">
         <v>6</v>
       </c>
       <c r="C24" t="s">
         <v>160</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="31" t="s">
         <v>171</v>
       </c>
     </row>
@@ -7907,7 +9218,7 @@
       <c r="C25" t="s">
         <v>161</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="31" t="s">
         <v>168</v>
       </c>
     </row>
@@ -7918,18 +9229,18 @@
       <c r="C26" t="s">
         <v>162</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="31" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="27" spans="2:4">
+    <row r="27" spans="2:4" ht="29">
       <c r="B27">
         <v>9</v>
       </c>
       <c r="C27" t="s">
         <v>163</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="31" t="s">
         <v>170</v>
       </c>
     </row>
@@ -7937,114 +9248,114 @@
       <c r="B29" s="4">
         <v>10</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" spans="2:4">
+      <c r="D29" s="79"/>
+    </row>
+    <row r="30" spans="2:4" ht="29">
       <c r="B30" s="4" t="s">
         <v>192</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="81" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="31" spans="2:4">
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="82" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="32" spans="2:4">
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="82" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="16"/>
-    </row>
-    <row r="34" spans="2:4">
+      <c r="D33" s="82"/>
+    </row>
+    <row r="34" spans="2:4" ht="29">
       <c r="B34" s="4" t="s">
         <v>193</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="82" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="79" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="36" spans="2:4">
+    <row r="36" spans="2:4" ht="29">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="82" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="16"/>
-    </row>
-    <row r="38" spans="2:4">
+      <c r="D37" s="82"/>
+    </row>
+    <row r="38" spans="2:4" ht="28">
       <c r="B38" s="4" t="s">
         <v>194</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="79" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="39" spans="2:4">
+    <row r="39" spans="2:4" ht="29">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="79" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="79" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="41" spans="2:4">
+    <row r="41" spans="2:4" ht="29">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="79" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="42" spans="2:4">
+    <row r="42" spans="2:4" ht="29">
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="79" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+      <c r="D43" s="79"/>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="4" t="s">
@@ -8053,35 +9364,35 @@
       <c r="C44" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="79" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="45" spans="2:4">
+    <row r="45" spans="2:4" ht="29">
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="79" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="46" spans="2:4">
+    <row r="46" spans="2:4" ht="29">
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="79" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="47" spans="2:4">
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="79" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="48" spans="2:4">
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
+      <c r="D48" s="79"/>
     </row>
     <row r="49" spans="2:4">
       <c r="B49" s="4" t="s">
@@ -8090,49 +9401,49 @@
       <c r="C49" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="79" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="50" spans="2:4">
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="79" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="51" spans="2:4">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
-      <c r="D51" s="37" t="s">
+      <c r="D51" s="83" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="52" spans="2:4">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
-      <c r="D52" s="37" t="s">
+      <c r="D52" s="83" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="53" spans="2:4">
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
-      <c r="D53" s="37" t="s">
+      <c r="D53" s="83" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="54" spans="2:4">
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="79" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="55" spans="2:4">
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
+      <c r="D55" s="79"/>
     </row>
     <row r="56" spans="2:4">
       <c r="B56" s="4" t="s">
@@ -8141,35 +9452,35 @@
       <c r="C56" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="D56" s="37" t="s">
+      <c r="D56" s="83" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="57" spans="2:4">
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="79" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="58" spans="2:4">
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
-      <c r="D58" s="37" t="s">
+      <c r="D58" s="83" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="59" spans="2:4">
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="79" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="60" spans="2:4">
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
+      <c r="D60" s="79"/>
     </row>
     <row r="62" spans="2:4">
       <c r="B62">
@@ -8178,12 +9489,12 @@
       <c r="C62" t="s">
         <v>402</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="79" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="63" spans="2:4">
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="79" t="s">
         <v>405</v>
       </c>
     </row>
@@ -8191,35 +9502,35 @@
       <c r="B64">
         <v>12</v>
       </c>
-      <c r="C64" s="38" t="s">
+      <c r="C64" s="33" t="s">
         <v>406</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="31" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="65" spans="2:4">
-      <c r="D65" t="s">
+      <c r="D65" s="31" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="66" spans="2:4">
-      <c r="D66" t="s">
+      <c r="D66" s="31" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="67" spans="2:4">
-      <c r="D67" t="s">
+      <c r="D67" s="31" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="68" spans="2:4">
-      <c r="D68" t="s">
+      <c r="D68" s="31" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="69" spans="2:4">
-      <c r="D69" t="s">
+      <c r="D69" s="31" t="s">
         <v>419</v>
       </c>
     </row>
@@ -8227,35 +9538,35 @@
       <c r="B71">
         <v>13</v>
       </c>
-      <c r="C71" s="38" t="s">
+      <c r="C71" s="33" t="s">
         <v>414</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="31" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="72" spans="2:4">
-      <c r="D72" t="s">
+      <c r="D72" s="31" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="73" spans="2:4">
-      <c r="D73" t="s">
+      <c r="D73" s="31" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="74" spans="2:4">
-      <c r="D74" t="s">
+      <c r="D74" s="31" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="75" spans="2:4">
-      <c r="D75" t="s">
+      <c r="D75" s="31" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="76" spans="2:4">
-      <c r="D76" t="s">
+      <c r="D76" s="31" t="s">
         <v>425</v>
       </c>
     </row>
@@ -8266,58 +9577,58 @@
       <c r="C78" t="s">
         <v>411</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="31" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="79" spans="2:4">
-      <c r="D79" t="s">
+      <c r="D79" s="31" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="80" spans="2:4">
-      <c r="D80" s="38" t="s">
+      <c r="D80" s="84" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="81" spans="2:4">
-      <c r="D81" s="38" t="s">
+      <c r="D81" s="84" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="82" spans="2:4">
-      <c r="D82" s="38" t="s">
+      <c r="D82" s="84" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="83" spans="2:4">
-      <c r="D83" s="38" t="s">
+      <c r="D83" s="84" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="85" spans="2:4">
+    <row r="85" spans="2:4" ht="29">
       <c r="B85">
         <v>15</v>
       </c>
       <c r="C85" t="s">
         <v>427</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="31" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="86" spans="2:4">
-      <c r="D86" t="s">
+      <c r="D86" s="31" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="87" spans="2:4">
-      <c r="D87" t="s">
+      <c r="D87" s="31" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="88" spans="2:4">
-      <c r="D88" t="s">
+      <c r="D88" s="31" t="s">
         <v>430</v>
       </c>
     </row>
@@ -8328,23 +9639,23 @@
       <c r="C90" t="s">
         <v>415</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="31" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="91" spans="2:4">
-      <c r="D91" t="s">
+      <c r="D91" s="31" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="93" spans="2:4">
+    <row r="93" spans="2:4" ht="29">
       <c r="B93">
         <v>17</v>
       </c>
       <c r="C93" t="s">
         <v>435</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="31" t="s">
         <v>436</v>
       </c>
     </row>
@@ -8355,12 +9666,12 @@
       <c r="C95" t="s">
         <v>437</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="31" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="96" spans="2:4">
-      <c r="D96" t="s">
+      <c r="D96" s="31" t="s">
         <v>439</v>
       </c>
     </row>
@@ -8371,12 +9682,12 @@
       <c r="C98" t="s">
         <v>444</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="31" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="99" spans="2:4">
-      <c r="D99" t="s">
+      <c r="D99" s="31" t="s">
         <v>441</v>
       </c>
     </row>
@@ -8387,38 +9698,38 @@
       <c r="C101" t="s">
         <v>442</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="31" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="102" spans="2:4">
-      <c r="D102" t="s">
+      <c r="D102" s="31" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="104" spans="2:4">
+    <row r="104" spans="2:4" ht="29">
       <c r="B104">
         <v>21</v>
       </c>
       <c r="C104" t="s">
         <v>446</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="31" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="105" spans="2:4">
-      <c r="D105" t="s">
+    <row r="105" spans="2:4" ht="29">
+      <c r="D105" s="31" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="106" spans="2:4">
-      <c r="D106" t="s">
+    <row r="106" spans="2:4" ht="29">
+      <c r="D106" s="31" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="107" spans="2:4">
-      <c r="D107" t="s">
+    <row r="107" spans="2:4" ht="29">
+      <c r="D107" s="31" t="s">
         <v>450</v>
       </c>
     </row>
@@ -8429,7 +9740,7 @@
       <c r="C109" t="s">
         <v>451</v>
       </c>
-      <c r="D109" s="38" t="s">
+      <c r="D109" s="84" t="s">
         <v>452</v>
       </c>
     </row>
@@ -8440,12 +9751,12 @@
       <c r="C110" t="s">
         <v>453</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D110" s="31" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="111" spans="2:4">
-      <c r="D111" s="39" t="s">
+      <c r="D111" s="71" t="s">
         <v>455</v>
       </c>
     </row>
@@ -8456,37 +9767,37 @@
       <c r="C112" t="s">
         <v>456</v>
       </c>
-      <c r="D112" s="40" t="s">
+      <c r="D112" s="85" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="113" spans="2:4">
-      <c r="D113" s="39" t="s">
+      <c r="D113" s="71" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="114" spans="2:4">
-      <c r="D114" s="40" t="s">
+      <c r="D114" s="85" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="115" spans="2:4">
-      <c r="D115" s="39" t="s">
+      <c r="D115" s="71" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="116" spans="2:4">
-      <c r="D116" s="40" t="s">
+      <c r="D116" s="85" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="117" spans="2:4">
-      <c r="D117" s="39" t="s">
+      <c r="D117" s="71" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="118" spans="2:4">
-      <c r="D118" s="40"/>
+      <c r="D118" s="85"/>
     </row>
     <row r="119" spans="2:4">
       <c r="B119">
@@ -8495,12 +9806,12 @@
       <c r="C119" t="s">
         <v>463</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D119" s="31" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="120" spans="2:4">
-      <c r="D120" t="s">
+      <c r="D120" s="31" t="s">
         <v>465</v>
       </c>
     </row>
@@ -8508,12 +9819,12 @@
       <c r="C121" t="s">
         <v>468</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D121" s="31" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="122" spans="2:4">
-      <c r="D122" t="s">
+      <c r="D122" s="31" t="s">
         <v>467</v>
       </c>
     </row>
@@ -8524,12 +9835,12 @@
       <c r="C124" t="s">
         <v>469</v>
       </c>
-      <c r="D124" s="35" t="s">
+      <c r="D124" s="31" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="125" spans="2:4">
-      <c r="D125" t="s">
+      <c r="D125" s="31" t="s">
         <v>470</v>
       </c>
     </row>
@@ -8540,27 +9851,27 @@
       <c r="C126" t="s">
         <v>478</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D126" s="31" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="127" spans="2:4">
-      <c r="D127" t="s">
+      <c r="D127" s="31" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="128" spans="2:4">
-      <c r="D128" s="41" t="s">
+      <c r="D128" s="86" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="129" spans="2:4">
-      <c r="D129" s="41" t="s">
+      <c r="D129" s="86" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="130" spans="2:4">
-      <c r="D130" t="s">
+      <c r="D130" s="31" t="s">
         <v>476</v>
       </c>
     </row>
@@ -8576,37 +9887,37 @@
       <c r="C132" t="s">
         <v>479</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" s="31" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="133" spans="2:4">
-      <c r="D133" t="s">
+      <c r="D133" s="31" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="134" spans="2:4">
-      <c r="D134" s="41" t="s">
+      <c r="D134" s="86" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="135" spans="2:4">
-      <c r="D135" s="41" t="s">
+      <c r="D135" s="86" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="136" spans="2:4">
-      <c r="D136" s="41" t="s">
+      <c r="D136" s="86" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="137" spans="2:4">
-      <c r="D137" s="40" t="s">
+      <c r="D137" s="85" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="138" spans="2:4">
-      <c r="D138" t="s">
+      <c r="D138" s="31" t="s">
         <v>485</v>
       </c>
     </row>
@@ -8617,37 +9928,37 @@
       <c r="C140" t="s">
         <v>486</v>
       </c>
-      <c r="D140" t="s">
+      <c r="D140" s="31" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="141" spans="2:4">
-      <c r="D141" s="36" t="s">
+      <c r="D141" s="40" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="142" spans="2:4">
-      <c r="D142" s="36" t="s">
+      <c r="D142" s="40" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="143" spans="2:4">
-      <c r="D143" s="36" t="s">
+      <c r="D143" s="40" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="144" spans="2:4">
-      <c r="D144" s="36" t="s">
+      <c r="D144" s="40" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="145" spans="2:4">
-      <c r="D145" t="s">
+      <c r="D145" s="31" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="146" spans="2:4">
-      <c r="D146" t="s">
+      <c r="D146" s="31" t="s">
         <v>493</v>
       </c>
     </row>
@@ -8658,124 +9969,124 @@
       <c r="C148" t="s">
         <v>497</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D148" s="31" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="D149" t="s">
+    <row r="149" spans="2:4" ht="29">
+      <c r="D149" s="31" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="150" spans="2:4">
-      <c r="C150" s="36" t="s">
+      <c r="C150" s="32" t="s">
         <v>500</v>
       </c>
-      <c r="D150" t="s">
+      <c r="D150" s="31" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="151" spans="2:4">
-      <c r="D151" t="s">
+      <c r="D151" s="31" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="152" spans="2:4">
-      <c r="D152" t="s">
+      <c r="D152" s="31" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="153" spans="2:4">
-      <c r="D153" t="s">
+      <c r="D153" s="31" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="154" spans="2:4">
-      <c r="D154" t="s">
+      <c r="D154" s="31" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="155" spans="2:4">
-      <c r="D155" t="s">
+      <c r="D155" s="31" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="156" spans="2:4">
-      <c r="D156" t="s">
+      <c r="D156" s="31" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="157" spans="2:4">
-      <c r="D157" t="s">
+      <c r="D157" s="31" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="158" spans="2:4">
-      <c r="D158" t="s">
+      <c r="D158" s="31" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="159" spans="2:4">
-      <c r="D159" t="s">
+      <c r="D159" s="31" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="161" spans="2:4">
-      <c r="C161" s="36" t="s">
+      <c r="C161" s="32" t="s">
         <v>516</v>
       </c>
-      <c r="D161" s="2" t="s">
+      <c r="D161" s="87" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="162" spans="2:4">
-      <c r="D162" s="39" t="s">
+      <c r="D162" s="71" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="163" spans="2:4">
-      <c r="D163" s="39" t="s">
+      <c r="D163" s="71" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="164" spans="2:4">
-      <c r="D164" s="39" t="s">
+      <c r="D164" s="71" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="165" spans="2:4">
-      <c r="D165" s="39" t="s">
+      <c r="D165" s="71" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="166" spans="2:4">
-      <c r="D166" s="39" t="s">
+    <row r="166" spans="2:4" ht="29">
+      <c r="D166" s="71" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="167" spans="2:4">
-      <c r="D167" s="39"/>
+      <c r="D167" s="71"/>
     </row>
     <row r="168" spans="2:4">
-      <c r="C168" s="36" t="s">
+      <c r="C168" s="32" t="s">
         <v>518</v>
       </c>
-      <c r="D168" t="s">
+      <c r="D168" s="31" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="169" spans="2:4">
-      <c r="D169" t="s">
+      <c r="D169" s="31" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="170" spans="2:4">
-      <c r="D170" t="s">
+      <c r="D170" s="31" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="171" spans="2:4">
-      <c r="D171" t="s">
+      <c r="D171" s="31" t="s">
         <v>522</v>
       </c>
     </row>
@@ -8786,48 +10097,48 @@
       <c r="C173" t="s">
         <v>523</v>
       </c>
-      <c r="D173" t="s">
+      <c r="D173" s="31" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="174" spans="2:4">
-      <c r="D174" t="s">
+      <c r="D174" s="31" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="176" spans="2:4">
+    <row r="176" spans="2:4" ht="29">
       <c r="B176">
         <v>32</v>
       </c>
       <c r="C176" t="s">
         <v>526</v>
       </c>
-      <c r="D176" t="s">
+      <c r="D176" s="31" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="177" spans="2:4">
-      <c r="D177" s="39" t="s">
+      <c r="D177" s="71" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="178" spans="2:4">
-      <c r="D178" s="39" t="s">
+      <c r="D178" s="71" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="179" spans="2:4">
-      <c r="D179" s="39" t="s">
+      <c r="D179" s="71" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="180" spans="2:4">
-      <c r="D180" t="s">
+    <row r="180" spans="2:4" ht="29">
+      <c r="D180" s="31" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="181" spans="2:4">
-      <c r="D181" t="s">
+      <c r="D181" s="31" t="s">
         <v>532</v>
       </c>
     </row>
@@ -8835,83 +10146,83 @@
       <c r="B183">
         <v>33</v>
       </c>
-      <c r="C183" s="36" t="s">
+      <c r="C183" s="32" t="s">
         <v>533</v>
       </c>
-      <c r="D183" t="s">
+      <c r="D183" s="31" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="185" spans="2:4" ht="28">
+    <row r="185" spans="2:4" ht="42">
       <c r="B185">
         <v>34</v>
       </c>
-      <c r="C185" s="42" t="s">
+      <c r="C185" s="35" t="s">
         <v>535</v>
       </c>
-      <c r="D185" s="44" t="s">
+      <c r="D185" s="88" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="186" spans="2:4">
-      <c r="C186" s="43"/>
-      <c r="D186" s="44" t="s">
+    <row r="186" spans="2:4" ht="28">
+      <c r="C186" s="36"/>
+      <c r="D186" s="88" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="187" spans="2:4">
-      <c r="C187" s="43"/>
-      <c r="D187" s="44" t="s">
+    <row r="187" spans="2:4" ht="28">
+      <c r="C187" s="36"/>
+      <c r="D187" s="88" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="188" spans="2:4">
-      <c r="D188" t="s">
+      <c r="D188" s="31" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="189" spans="2:4">
-      <c r="D189" t="s">
+      <c r="D189" s="31" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="190" spans="2:4">
-      <c r="D190" t="s">
+      <c r="D190" s="31" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="191" spans="2:4">
-      <c r="D191" t="s">
+      <c r="D191" s="31" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="192" spans="2:4" ht="16">
-      <c r="D192" s="45" t="s">
+    <row r="192" spans="2:4" ht="32">
+      <c r="D192" s="37" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="193" spans="2:4" ht="16">
-      <c r="D193" s="46" t="s">
+      <c r="D193" s="38" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="194" spans="2:4" ht="16">
-      <c r="D194" s="46" t="s">
+      <c r="D194" s="38" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="195" spans="2:4" ht="16">
-      <c r="D195" s="46" t="s">
+      <c r="D195" s="38" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="196" spans="2:4" ht="16">
-      <c r="D196" s="46" t="s">
+      <c r="D196" s="38" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="197" spans="2:4" ht="16">
-      <c r="D197" s="46" t="s">
+      <c r="D197" s="38" t="s">
         <v>99</v>
       </c>
     </row>
@@ -8919,66 +10230,66 @@
       <c r="B199">
         <v>35</v>
       </c>
-      <c r="C199" s="36" t="s">
+      <c r="C199" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="D199" s="47" t="s">
+      <c r="D199" s="37" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="200" spans="2:4" ht="16">
-      <c r="D200" s="47" t="s">
+      <c r="D200" s="37" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="201" spans="2:4" ht="16">
-      <c r="D201" s="47" t="s">
+      <c r="D201" s="37" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="202" spans="2:4" ht="16">
-      <c r="D202" s="47" t="s">
+      <c r="D202" s="37" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="203" spans="2:4" ht="16">
-      <c r="D203" s="47" t="s">
+      <c r="D203" s="37" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="204" spans="2:4" ht="16">
-      <c r="D204" s="48" t="s">
+      <c r="D204" s="38" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="205" spans="2:4" ht="16">
-      <c r="D205" s="49" t="s">
+      <c r="D205" s="38" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="206" spans="2:4" ht="16">
-      <c r="D206" s="49" t="s">
+      <c r="D206" s="38" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="207" spans="2:4" ht="16">
-      <c r="D207" s="49" t="s">
+      <c r="D207" s="38" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="208" spans="2:4" ht="16">
-      <c r="D208" s="49" t="s">
+      <c r="D208" s="38" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="210" spans="2:4" ht="16">
+    <row r="210" spans="2:4" ht="32">
       <c r="B210">
         <v>36</v>
       </c>
       <c r="C210" t="s">
         <v>159</v>
       </c>
-      <c r="D210" s="50" t="s">
+      <c r="D210" s="89" t="s">
         <v>558</v>
       </c>
     </row>
@@ -8989,27 +10300,27 @@
       <c r="C212" t="s">
         <v>559</v>
       </c>
-      <c r="D212" s="48" t="s">
+      <c r="D212" s="38" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="213" spans="2:4" ht="16">
-      <c r="D213" s="48" t="s">
+      <c r="D213" s="38" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="214" spans="2:4" ht="16">
-      <c r="D214" s="48" t="s">
+      <c r="D214" s="38" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="215" spans="2:4" ht="16">
-      <c r="D215" s="48" t="s">
+      <c r="D215" s="38" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="216" spans="2:4" ht="16">
-      <c r="D216" s="48" t="s">
+      <c r="D216" s="38" t="s">
         <v>564</v>
       </c>
     </row>
@@ -9020,7 +10331,7 @@
       <c r="C219" t="s">
         <v>565</v>
       </c>
-      <c r="D219" t="s">
+      <c r="D219" s="31" t="s">
         <v>566</v>
       </c>
     </row>
@@ -9031,32 +10342,32 @@
       <c r="C221" t="s">
         <v>567</v>
       </c>
-      <c r="D221" s="50" t="s">
+      <c r="D221" s="89" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="222" spans="2:4" ht="16">
-      <c r="D222" s="50" t="s">
+      <c r="D222" s="89" t="s">
         <v>569</v>
       </c>
     </row>
     <row r="223" spans="2:4" ht="16">
-      <c r="D223" s="47" t="s">
+      <c r="D223" s="37" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="224" spans="2:4" ht="16">
-      <c r="D224" s="47" t="s">
+      <c r="D224" s="37" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="225" spans="2:4" ht="16">
-      <c r="D225" s="47" t="s">
+      <c r="D225" s="37" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="226" spans="2:4" ht="16">
-      <c r="D226" s="47" t="s">
+      <c r="D226" s="37" t="s">
         <v>573</v>
       </c>
     </row>
@@ -9067,7 +10378,7 @@
       <c r="C228" t="s">
         <v>574</v>
       </c>
-      <c r="D228" s="47" t="s">
+      <c r="D228" s="37" t="s">
         <v>575</v>
       </c>
     </row>
@@ -9075,42 +10386,42 @@
       <c r="C230" t="s">
         <v>576</v>
       </c>
-      <c r="D230" s="45" t="s">
+      <c r="D230" s="37" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="231" spans="2:4" ht="16">
-      <c r="D231" s="46" t="s">
+      <c r="D231" s="38" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="232" spans="2:4" ht="16">
-      <c r="D232" s="45" t="s">
+      <c r="D232" s="37" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="233" spans="2:4" ht="16">
-      <c r="D233" s="46" t="s">
+      <c r="D233" s="38" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="234" spans="2:4" ht="16">
-      <c r="D234" s="45" t="s">
+      <c r="D234" s="37" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="235" spans="2:4" ht="16">
-      <c r="D235" s="46" t="s">
+    <row r="235" spans="2:4" ht="29">
+      <c r="D235" s="38" t="s">
         <v>582</v>
       </c>
     </row>
     <row r="236" spans="2:4" ht="16">
-      <c r="D236" s="45" t="s">
+      <c r="D236" s="37" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="237" spans="2:4" ht="16">
-      <c r="D237" s="45" t="s">
+      <c r="D237" s="37" t="s">
         <v>584</v>
       </c>
     </row>
@@ -9118,12 +10429,12 @@
       <c r="C239" t="s">
         <v>585</v>
       </c>
-      <c r="D239" s="50" t="s">
+      <c r="D239" s="89" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="240" spans="2:4" ht="16">
-      <c r="D240" s="50" t="s">
+      <c r="D240" s="89" t="s">
         <v>587</v>
       </c>
     </row>
@@ -9134,43 +10445,43 @@
       <c r="C242" t="s">
         <v>588</v>
       </c>
-      <c r="D242" s="51" t="s">
+      <c r="D242" s="39" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="243" spans="2:4" ht="16">
-      <c r="D243" s="51" t="s">
+      <c r="D243" s="39" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="244" spans="2:4" ht="16">
-      <c r="D244" s="51" t="s">
+      <c r="D244" s="39" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="245" spans="2:4" ht="16">
-      <c r="D245" s="51" t="s">
+      <c r="D245" s="39" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="247" spans="2:4">
+    <row r="247" spans="2:4" ht="26">
       <c r="B247">
         <v>42</v>
       </c>
       <c r="C247" t="s">
         <v>593</v>
       </c>
-      <c r="D247" s="51" t="s">
+      <c r="D247" s="39" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="248" spans="2:4">
-      <c r="D248" t="s">
+      <c r="D248" s="31" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="249" spans="2:4">
-      <c r="D249" s="51" t="s">
+      <c r="D249" s="39" t="s">
         <v>596</v>
       </c>
     </row>
@@ -9178,61 +10489,61 @@
       <c r="B251">
         <v>43</v>
       </c>
-      <c r="C251" s="36" t="s">
+      <c r="C251" s="32" t="s">
         <v>597</v>
       </c>
-      <c r="D251" t="s">
+      <c r="D251" s="31" t="s">
         <v>598</v>
       </c>
     </row>
     <row r="252" spans="2:4">
-      <c r="D252" t="s">
+      <c r="D252" s="31" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="254" spans="2:4">
-      <c r="D254" s="36" t="s">
+      <c r="D254" s="40" t="s">
         <v>600</v>
       </c>
     </row>
     <row r="256" spans="2:4">
-      <c r="D256" s="36" t="s">
+      <c r="D256" s="40" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="257" spans="2:4">
-      <c r="D257" t="s">
+      <c r="D257" s="31" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="258" spans="2:4">
-      <c r="D258" t="s">
+      <c r="D258" s="31" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="259" spans="2:4">
-      <c r="D259" s="39" t="s">
+      <c r="D259" s="71" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="261" spans="2:4">
+    <row r="261" spans="2:4" ht="29">
       <c r="B261">
         <v>44</v>
       </c>
       <c r="C261" t="s">
         <v>607</v>
       </c>
-      <c r="D261" t="s">
+      <c r="D261" s="31" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="262" spans="2:4">
-      <c r="D262" t="s">
+    <row r="262" spans="2:4" ht="29">
+      <c r="D262" s="31" t="s">
         <v>606</v>
       </c>
     </row>
     <row r="263" spans="2:4">
-      <c r="D263" s="39"/>
+      <c r="D263" s="71"/>
     </row>
     <row r="264" spans="2:4">
       <c r="B264">
@@ -9241,17 +10552,17 @@
       <c r="C264" t="s">
         <v>608</v>
       </c>
-      <c r="D264" s="52" t="s">
+      <c r="D264" s="71" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="265" spans="2:4">
-      <c r="D265" s="52" t="s">
+    <row r="265" spans="2:4" ht="29">
+      <c r="D265" s="71" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="266" spans="2:4">
-      <c r="D266" s="52"/>
+      <c r="D266" s="71"/>
     </row>
     <row r="267" spans="2:4">
       <c r="B267">
@@ -9260,7 +10571,7 @@
       <c r="C267" t="s">
         <v>612</v>
       </c>
-      <c r="D267" t="s">
+      <c r="D267" s="31" t="s">
         <v>611</v>
       </c>
     </row>
@@ -9271,203 +10582,203 @@
       <c r="C269" t="s">
         <v>613</v>
       </c>
-      <c r="D269" t="s">
+      <c r="D269" s="31" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="270" spans="2:4">
-      <c r="D270" t="s">
+    <row r="270" spans="2:4" ht="29">
+      <c r="D270" s="31" t="s">
         <v>615</v>
       </c>
     </row>
     <row r="271" spans="2:4">
-      <c r="D271" s="39" t="s">
+      <c r="D271" s="71" t="s">
         <v>616</v>
       </c>
     </row>
     <row r="272" spans="2:4">
-      <c r="D272" s="5"/>
-    </row>
-    <row r="273" spans="3:4">
-      <c r="C273" s="54" t="s">
+      <c r="D272" s="54"/>
+    </row>
+    <row r="273" spans="3:4" ht="25">
+      <c r="C273" s="40" t="s">
         <v>617</v>
       </c>
-      <c r="D273" s="53" t="s">
+      <c r="D273" s="55" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="274" spans="3:4">
-      <c r="D274" s="53"/>
+      <c r="D274" s="55"/>
     </row>
     <row r="275" spans="3:4">
-      <c r="D275" s="57" t="s">
+      <c r="D275" s="90" t="s">
         <v>619</v>
       </c>
     </row>
     <row r="276" spans="3:4">
-      <c r="D276" s="57" t="s">
+      <c r="D276" s="90" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="277" spans="3:4">
-      <c r="D277" s="57" t="s">
+      <c r="D277" s="90" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="279" spans="3:4">
+    <row r="279" spans="3:4" ht="29">
       <c r="C279" t="s">
         <v>621</v>
       </c>
-      <c r="D279" t="s">
+      <c r="D279" s="31" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="280" spans="3:4">
-      <c r="D280" s="57" t="s">
+      <c r="D280" s="90" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="281" spans="3:4">
-      <c r="D281" s="57" t="s">
+      <c r="D281" s="90" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="282" spans="3:4">
-      <c r="D282" s="57" t="s">
+      <c r="D282" s="90" t="s">
         <v>625</v>
       </c>
     </row>
     <row r="283" spans="3:4">
-      <c r="D283" s="57" t="s">
+      <c r="D283" s="90" t="s">
         <v>626</v>
       </c>
     </row>
     <row r="284" spans="3:4">
-      <c r="D284" s="57" t="s">
+      <c r="D284" s="90" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="286" spans="3:4" ht="29">
+    <row r="286" spans="3:4" ht="43.5">
       <c r="C286" t="s">
         <v>627</v>
       </c>
-      <c r="D286" s="35" t="s">
+      <c r="D286" s="31" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="288" spans="3:4">
-      <c r="D288" s="57" t="s">
+      <c r="D288" s="90" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="289" spans="2:4">
-      <c r="D289" s="57" t="s">
+      <c r="D289" s="90" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="290" spans="2:4">
-      <c r="D290" s="57" t="s">
+      <c r="D290" s="90" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="292" spans="2:4">
+    <row r="292" spans="2:4" ht="29">
       <c r="C292" t="s">
         <v>631</v>
       </c>
-      <c r="D292" t="s">
+      <c r="D292" s="31" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="293" spans="2:4">
-      <c r="D293" t="s">
+      <c r="D293" s="31" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="295" spans="2:4">
+    <row r="295" spans="2:4" ht="29">
       <c r="B295">
         <v>48</v>
       </c>
-      <c r="C295" s="55" t="s">
+      <c r="C295" s="41" t="s">
         <v>633</v>
       </c>
-      <c r="D295" t="s">
+      <c r="D295" s="31" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="296" spans="2:4">
-      <c r="D296" t="s">
+    <row r="296" spans="2:4" ht="29">
+      <c r="D296" s="31" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="297" spans="2:4">
-      <c r="D297" s="56" t="s">
+      <c r="D297" s="91" t="s">
         <v>636</v>
       </c>
     </row>
     <row r="298" spans="2:4">
-      <c r="D298" s="56" t="s">
+      <c r="D298" s="91" t="s">
         <v>637</v>
       </c>
     </row>
     <row r="299" spans="2:4">
-      <c r="D299" s="56" t="s">
+      <c r="D299" s="91" t="s">
         <v>638</v>
       </c>
     </row>
     <row r="300" spans="2:4">
-      <c r="D300" s="56" t="s">
+      <c r="D300" s="91" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="301" spans="2:4">
-      <c r="D301" s="39"/>
-    </row>
-    <row r="302" spans="2:4">
+      <c r="D301" s="71"/>
+    </row>
+    <row r="302" spans="2:4" ht="29">
       <c r="C302" t="s">
         <v>640</v>
       </c>
-      <c r="D302" t="s">
+      <c r="D302" s="31" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="303" spans="2:4">
-      <c r="D303" s="39"/>
+      <c r="D303" s="71"/>
     </row>
     <row r="304" spans="2:4">
-      <c r="D304" s="57" t="s">
+      <c r="D304" s="90" t="s">
         <v>642</v>
       </c>
     </row>
     <row r="305" spans="3:4">
-      <c r="D305" s="57" t="s">
+      <c r="D305" s="90" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="306" spans="3:4">
-      <c r="D306" s="57" t="s">
+      <c r="D306" s="90" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="308" spans="3:4">
+    <row r="308" spans="3:4" ht="29">
       <c r="C308" t="s">
         <v>637</v>
       </c>
-      <c r="D308" t="s">
+      <c r="D308" s="31" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="310" spans="3:4">
-      <c r="D310" s="57" t="s">
+      <c r="D310" s="90" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="311" spans="3:4">
-      <c r="D311" s="57" t="s">
+      <c r="D311" s="90" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="312" spans="3:4">
-      <c r="D312" s="57" t="s">
+      <c r="D312" s="90" t="s">
         <v>542</v>
       </c>
     </row>
@@ -9475,90 +10786,90 @@
       <c r="C314" t="s">
         <v>638</v>
       </c>
-      <c r="D314" t="s">
+      <c r="D314" s="31" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="315" spans="3:4">
-      <c r="D315" t="s">
+    <row r="315" spans="3:4" ht="29">
+      <c r="D315" s="31" t="s">
         <v>646</v>
       </c>
     </row>
     <row r="317" spans="3:4">
-      <c r="D317" s="57" t="s">
+      <c r="D317" s="90" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="318" spans="3:4">
-      <c r="D318" s="57" t="s">
+      <c r="D318" s="90" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="319" spans="3:4">
-      <c r="D319" s="57" t="s">
+      <c r="D319" s="90" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="321" spans="2:4" ht="29">
-      <c r="C321" s="35" t="s">
+    <row r="321" spans="2:4" ht="43.5">
+      <c r="C321" s="31" t="s">
         <v>639</v>
       </c>
-      <c r="D321" s="35" t="s">
+      <c r="D321" s="31" t="s">
         <v>648</v>
       </c>
     </row>
     <row r="323" spans="2:4">
-      <c r="D323" s="57" t="s">
+      <c r="D323" s="90" t="s">
         <v>649</v>
       </c>
     </row>
     <row r="324" spans="2:4">
-      <c r="D324" s="57" t="s">
+      <c r="D324" s="90" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="325" spans="2:4">
-      <c r="D325" s="57" t="s">
+      <c r="D325" s="90" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="328" spans="2:4">
-      <c r="C328" s="58" t="s">
+      <c r="C328" s="42" t="s">
         <v>597</v>
       </c>
-      <c r="D328" s="58" t="s">
+      <c r="D328" s="42" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="329" spans="2:4">
-      <c r="C329" s="59" t="s">
+      <c r="C329" s="43" t="s">
         <v>656</v>
       </c>
-      <c r="D329" s="60" t="s">
+      <c r="D329" s="44" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="330" spans="2:4">
-      <c r="C330" s="59" t="s">
+      <c r="C330" s="43" t="s">
         <v>658</v>
       </c>
-      <c r="D330" s="60" t="s">
+      <c r="D330" s="44" t="s">
         <v>659</v>
       </c>
     </row>
     <row r="331" spans="2:4">
-      <c r="C331" s="59" t="s">
+      <c r="C331" s="43" t="s">
         <v>660</v>
       </c>
-      <c r="D331" s="60" t="s">
+      <c r="D331" s="44" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="332" spans="2:4">
-      <c r="C332" s="59" t="s">
+      <c r="C332" s="43" t="s">
         <v>662</v>
       </c>
-      <c r="D332" s="60" t="s">
+      <c r="D332" s="44" t="s">
         <v>663</v>
       </c>
     </row>
@@ -9566,36 +10877,36 @@
       <c r="B334">
         <v>49</v>
       </c>
-      <c r="C334" s="55" t="s">
+      <c r="C334" s="41" t="s">
         <v>650</v>
       </c>
-      <c r="D334" t="s">
+      <c r="D334" s="31" t="s">
         <v>651</v>
       </c>
     </row>
     <row r="335" spans="2:4">
-      <c r="D335" s="39" t="s">
+      <c r="D335" s="71" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="336" spans="2:4">
-      <c r="D336" s="39" t="s">
+      <c r="D336" s="71" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="337" spans="2:4">
-      <c r="D337" s="39" t="s">
+      <c r="D337" s="71" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="339" spans="2:4">
+    <row r="339" spans="2:4" ht="29">
       <c r="B339">
         <v>50</v>
       </c>
-      <c r="C339" s="36" t="s">
+      <c r="C339" s="32" t="s">
         <v>664</v>
       </c>
-      <c r="D339" s="39" t="s">
+      <c r="D339" s="71" t="s">
         <v>665</v>
       </c>
     </row>
@@ -9608,7 +10919,7 @@
       <c r="C341" t="s">
         <v>666</v>
       </c>
-      <c r="D341" t="s">
+      <c r="D341" s="31" t="s">
         <v>667</v>
       </c>
     </row>
@@ -9616,7 +10927,7 @@
       <c r="C342" t="s">
         <v>668</v>
       </c>
-      <c r="D342" t="s">
+      <c r="D342" s="31" t="s">
         <v>669</v>
       </c>
     </row>
@@ -9624,7 +10935,7 @@
       <c r="C343" t="s">
         <v>674</v>
       </c>
-      <c r="D343" t="s">
+      <c r="D343" s="31" t="s">
         <v>670</v>
       </c>
     </row>
@@ -9632,7 +10943,7 @@
       <c r="C344" t="s">
         <v>675</v>
       </c>
-      <c r="D344" t="s">
+      <c r="D344" s="31" t="s">
         <v>671</v>
       </c>
     </row>
@@ -9640,7 +10951,7 @@
       <c r="C345" t="s">
         <v>673</v>
       </c>
-      <c r="D345" t="s">
+      <c r="D345" s="31" t="s">
         <v>672</v>
       </c>
     </row>
@@ -9648,17 +10959,17 @@
       <c r="C347" t="s">
         <v>676</v>
       </c>
-      <c r="D347" t="s">
+      <c r="D347" s="31" t="s">
         <v>677</v>
       </c>
     </row>
     <row r="348" spans="2:4">
-      <c r="D348" t="s">
+      <c r="D348" s="31" t="s">
         <v>678</v>
       </c>
     </row>
     <row r="350" spans="2:4">
-      <c r="D350" s="57" t="s">
+      <c r="D350" s="90" t="s">
         <v>679</v>
       </c>
     </row>
@@ -9666,38 +10977,38 @@
       <c r="C352" t="s">
         <v>680</v>
       </c>
-      <c r="D352" t="s">
+      <c r="D352" s="31" t="s">
         <v>681</v>
       </c>
     </row>
     <row r="354" spans="2:4">
-      <c r="D354" s="57" t="s">
+      <c r="D354" s="90" t="s">
         <v>684</v>
       </c>
     </row>
     <row r="355" spans="2:4">
-      <c r="D355" s="57" t="s">
+      <c r="D355" s="90" t="s">
         <v>682</v>
       </c>
     </row>
     <row r="356" spans="2:4">
-      <c r="D356" s="57" t="s">
+      <c r="D356" s="90" t="s">
         <v>683</v>
       </c>
     </row>
     <row r="357" spans="2:4">
-      <c r="D357" s="57" t="s">
+      <c r="D357" s="90" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="359" spans="2:4" ht="48">
+    <row r="359" spans="2:4" ht="80">
       <c r="B359">
         <v>60</v>
       </c>
-      <c r="C359" s="61" t="s">
+      <c r="C359" s="45" t="s">
         <v>685</v>
       </c>
-      <c r="D359" s="63" t="s">
+      <c r="D359" s="47" t="s">
         <v>686</v>
       </c>
     </row>
@@ -9705,7 +11016,7 @@
       <c r="B363">
         <v>61</v>
       </c>
-      <c r="D363" s="55" t="s">
+      <c r="D363" s="92" t="s">
         <v>691</v>
       </c>
     </row>
@@ -9716,7 +11027,7 @@
       <c r="C365" t="s">
         <v>687</v>
       </c>
-      <c r="D365" t="s">
+      <c r="D365" s="31" t="s">
         <v>688</v>
       </c>
     </row>
@@ -9724,10 +11035,10 @@
       <c r="B366">
         <v>1000</v>
       </c>
-      <c r="C366" s="62" t="s">
+      <c r="C366" s="46" t="s">
         <v>689</v>
       </c>
-      <c r="D366" s="62" t="s">
+      <c r="D366" s="47" t="s">
         <v>696</v>
       </c>
     </row>
@@ -9738,7 +11049,7 @@
       <c r="C367" t="s">
         <v>693</v>
       </c>
-      <c r="D367" s="62" t="s">
+      <c r="D367" s="47" t="s">
         <v>700</v>
       </c>
     </row>
@@ -9749,7 +11060,7 @@
       <c r="C368" t="s">
         <v>694</v>
       </c>
-      <c r="D368" s="62" t="s">
+      <c r="D368" s="47" t="s">
         <v>697</v>
       </c>
     </row>
@@ -9760,7 +11071,7 @@
       <c r="C369" t="s">
         <v>690</v>
       </c>
-      <c r="D369" s="62" t="s">
+      <c r="D369" s="47" t="s">
         <v>698</v>
       </c>
     </row>
@@ -9771,15 +11082,15 @@
       <c r="C370" t="s">
         <v>695</v>
       </c>
-      <c r="D370" s="62" t="s">
+      <c r="D370" s="47" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="371" spans="2:4" ht="16">
-      <c r="D371" s="62"/>
-    </row>
-    <row r="372" spans="2:4" ht="16">
-      <c r="D372" s="64" t="s">
+      <c r="D371" s="47"/>
+    </row>
+    <row r="372" spans="2:4" ht="32">
+      <c r="D372" s="93" t="s">
         <v>702</v>
       </c>
     </row>
@@ -9790,7 +11101,7 @@
       <c r="C374" t="s">
         <v>701</v>
       </c>
-      <c r="D374" t="s">
+      <c r="D374" s="31" t="s">
         <v>703</v>
       </c>
     </row>
@@ -9798,21 +11109,21 @@
       <c r="B376">
         <v>63</v>
       </c>
-      <c r="C376" s="41" t="s">
+      <c r="C376" s="34" t="s">
         <v>704</v>
       </c>
-      <c r="D376" t="s">
+      <c r="D376" s="31" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="378" spans="2:4" ht="29">
+    <row r="378" spans="2:4" ht="43.5">
       <c r="B378">
         <v>64</v>
       </c>
-      <c r="C378" s="41" t="s">
+      <c r="C378" s="34" t="s">
         <v>707</v>
       </c>
-      <c r="D378" s="35" t="s">
+      <c r="D378" s="31" t="s">
         <v>706</v>
       </c>
     </row>
@@ -9820,90 +11131,90 @@
       <c r="B380">
         <v>65</v>
       </c>
-      <c r="C380" s="62" t="s">
+      <c r="C380" s="46" t="s">
         <v>708</v>
       </c>
-      <c r="D380" s="65" t="s">
+      <c r="D380" s="48" t="s">
         <v>709</v>
       </c>
     </row>
     <row r="381" spans="2:4" ht="16">
-      <c r="D381" s="65" t="s">
+      <c r="D381" s="48" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="382" spans="2:4" ht="16">
-      <c r="D382" s="65" t="s">
+      <c r="D382" s="48" t="s">
         <v>711</v>
       </c>
     </row>
     <row r="383" spans="2:4" ht="16">
-      <c r="D383" s="65" t="s">
+      <c r="D383" s="48" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="384" spans="2:4" ht="16">
-      <c r="D384" s="65" t="s">
+    <row r="384" spans="2:4" ht="32">
+      <c r="D384" s="48" t="s">
         <v>713</v>
       </c>
     </row>
     <row r="385" spans="2:4" ht="16">
-      <c r="D385" s="65" t="s">
+      <c r="D385" s="48" t="s">
         <v>714</v>
       </c>
     </row>
     <row r="386" spans="2:4" ht="16">
-      <c r="D386" s="65" t="s">
+      <c r="D386" s="48" t="s">
         <v>715</v>
       </c>
     </row>
     <row r="387" spans="2:4" ht="16">
-      <c r="D387" s="65" t="s">
+      <c r="D387" s="48" t="s">
         <v>716</v>
       </c>
     </row>
     <row r="388" spans="2:4" ht="16">
-      <c r="D388" s="65" t="s">
+      <c r="D388" s="48" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="389" spans="2:4" ht="16">
-      <c r="D389" s="65" t="s">
+      <c r="D389" s="48" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="390" spans="2:4" ht="16">
-      <c r="D390" s="65" t="s">
+    <row r="390" spans="2:4" ht="32">
+      <c r="D390" s="48" t="s">
         <v>719</v>
       </c>
     </row>
     <row r="391" spans="2:4" ht="16">
-      <c r="D391" s="65" t="s">
+      <c r="D391" s="48" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="392" spans="2:4" ht="16">
-      <c r="D392" s="65" t="s">
+      <c r="D392" s="48" t="s">
         <v>721</v>
       </c>
     </row>
     <row r="393" spans="2:4" ht="16">
-      <c r="D393" s="65" t="s">
+      <c r="D393" s="48" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="394" spans="2:4" ht="16">
-      <c r="D394" s="65" t="s">
+      <c r="D394" s="48" t="s">
         <v>723</v>
       </c>
     </row>
     <row r="395" spans="2:4" ht="16">
-      <c r="D395" s="65" t="s">
+      <c r="D395" s="48" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="396" spans="2:4" ht="16">
-      <c r="D396" s="65" t="s">
+      <c r="D396" s="48" t="s">
         <v>725</v>
       </c>
     </row>
@@ -9914,72 +11225,72 @@
       <c r="C398" t="s">
         <v>726</v>
       </c>
-      <c r="D398" s="66" t="s">
+      <c r="D398" s="94" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="399" spans="2:4" ht="16">
-      <c r="D399" s="66" t="s">
+      <c r="D399" s="94" t="s">
         <v>727</v>
       </c>
     </row>
     <row r="400" spans="2:4" ht="16">
-      <c r="D400" s="66" t="s">
+      <c r="D400" s="94" t="s">
         <v>728</v>
       </c>
     </row>
     <row r="401" spans="2:4" ht="16">
-      <c r="D401" s="66" t="s">
+      <c r="D401" s="94" t="s">
         <v>729</v>
       </c>
     </row>
     <row r="402" spans="2:4" ht="16">
-      <c r="D402" s="66" t="s">
+      <c r="D402" s="94" t="s">
         <v>730</v>
       </c>
     </row>
     <row r="403" spans="2:4" ht="16">
-      <c r="D403" s="66" t="s">
+      <c r="D403" s="94" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="404" spans="2:4" ht="16">
-      <c r="D404" s="66" t="s">
+      <c r="D404" s="94" t="s">
         <v>732</v>
       </c>
     </row>
     <row r="405" spans="2:4" ht="16">
-      <c r="D405" s="66" t="s">
+      <c r="D405" s="94" t="s">
         <v>733</v>
       </c>
     </row>
     <row r="406" spans="2:4" ht="16">
-      <c r="D406" s="66" t="s">
+      <c r="D406" s="94" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="407" spans="2:4" ht="16">
-      <c r="D407" s="66" t="s">
+      <c r="D407" s="94" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="408" spans="2:4" ht="16">
-      <c r="D408" s="66" t="s">
+      <c r="D408" s="94" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="409" spans="2:4" ht="16">
-      <c r="D409" s="66" t="s">
+      <c r="D409" s="94" t="s">
         <v>736</v>
       </c>
     </row>
     <row r="410" spans="2:4" ht="16">
-      <c r="D410" s="66" t="s">
+      <c r="D410" s="94" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="411" spans="2:4" ht="16">
-      <c r="D411" s="66" t="s">
+      <c r="D411" s="94" t="s">
         <v>738</v>
       </c>
     </row>
@@ -9987,51 +11298,51 @@
       <c r="B413">
         <v>67</v>
       </c>
-      <c r="C413" s="66" t="s">
+      <c r="C413" s="49" t="s">
         <v>739</v>
       </c>
-      <c r="D413" s="66" t="s">
+      <c r="D413" s="94" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="415" spans="2:4" ht="16">
+    <row r="415" spans="2:4" ht="32">
       <c r="B415">
         <v>68</v>
       </c>
       <c r="C415" t="s">
         <v>741</v>
       </c>
-      <c r="D415" s="62" t="s">
+      <c r="D415" s="47" t="s">
         <v>742</v>
       </c>
     </row>
     <row r="416" spans="2:4" ht="16">
-      <c r="D416" s="62" t="s">
+      <c r="D416" s="47" t="s">
         <v>743</v>
       </c>
     </row>
     <row r="417" spans="3:4" ht="16">
-      <c r="D417" s="62" t="s">
+      <c r="D417" s="47" t="s">
         <v>744</v>
       </c>
     </row>
     <row r="418" spans="3:4" ht="16">
-      <c r="D418" s="62" t="s">
+      <c r="D418" s="47" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="419" spans="3:4" ht="16">
-      <c r="D419" s="62" t="s">
+      <c r="D419" s="47" t="s">
         <v>746</v>
       </c>
     </row>
     <row r="420" spans="3:4" ht="16">
-      <c r="D420" s="62" t="s">
+      <c r="D420" s="47" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="421" spans="3:4" ht="16">
-      <c r="D421" s="62" t="s">
+      <c r="D421" s="47" t="s">
         <v>748</v>
       </c>
     </row>
@@ -10039,70 +11350,70 @@
       <c r="C423" t="s">
         <v>749</v>
       </c>
-      <c r="D423" s="62" t="s">
+      <c r="D423" s="47" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="424" spans="3:4" ht="16">
-      <c r="D424" s="62" t="s">
+    <row r="424" spans="3:4" ht="32">
+      <c r="D424" s="47" t="s">
         <v>751</v>
       </c>
     </row>
     <row r="425" spans="3:4" ht="16">
-      <c r="D425" s="62" t="s">
+      <c r="D425" s="47" t="s">
         <v>797</v>
       </c>
     </row>
     <row r="426" spans="3:4" ht="16">
-      <c r="D426" s="62" t="s">
+      <c r="D426" s="47" t="s">
         <v>752</v>
       </c>
     </row>
     <row r="427" spans="3:4" ht="16">
-      <c r="D427" s="62" t="s">
+      <c r="D427" s="47" t="s">
         <v>753</v>
       </c>
     </row>
     <row r="429" spans="3:4" ht="16">
-      <c r="D429" s="67" t="s">
+      <c r="D429" s="95" t="s">
         <v>758</v>
       </c>
     </row>
     <row r="430" spans="3:4" ht="16">
-      <c r="D430" s="67" t="s">
+      <c r="D430" s="95" t="s">
         <v>754</v>
       </c>
     </row>
     <row r="431" spans="3:4" ht="16">
-      <c r="D431" s="67" t="s">
+      <c r="D431" s="95" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="432" spans="3:4">
-      <c r="D432" s="68" t="s">
+    <row r="432" spans="3:4" ht="26.5">
+      <c r="D432" s="51" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="434" spans="3:4" ht="16">
+    <row r="434" spans="3:4" ht="32">
       <c r="C434" t="s">
         <v>757</v>
       </c>
-      <c r="D434" s="62" t="s">
+      <c r="D434" s="47" t="s">
         <v>759</v>
       </c>
     </row>
     <row r="435" spans="3:4" ht="16">
-      <c r="D435" s="62" t="s">
+      <c r="D435" s="47" t="s">
         <v>760</v>
       </c>
     </row>
     <row r="436" spans="3:4" ht="16">
-      <c r="D436" s="62" t="s">
+      <c r="D436" s="47" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="438" spans="3:4" ht="24.5">
-      <c r="D438" s="69" t="s">
+    <row r="438" spans="3:4" ht="48.5">
+      <c r="D438" s="50" t="s">
         <v>762</v>
       </c>
     </row>
@@ -10110,27 +11421,27 @@
       <c r="C440" t="s">
         <v>763</v>
       </c>
-      <c r="D440" s="62" t="s">
+      <c r="D440" s="47" t="s">
         <v>764</v>
       </c>
     </row>
     <row r="441" spans="3:4" ht="16">
-      <c r="D441" s="62" t="s">
+      <c r="D441" s="47" t="s">
         <v>765</v>
       </c>
     </row>
     <row r="442" spans="3:4" ht="16">
-      <c r="D442" s="62" t="s">
+      <c r="D442" s="47" t="s">
         <v>766</v>
       </c>
     </row>
     <row r="443" spans="3:4" ht="16">
-      <c r="D443" s="62" t="s">
+      <c r="D443" s="47" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="445" spans="3:4" ht="26.5">
-      <c r="D445" s="70" t="s">
+    <row r="445" spans="3:4" ht="52.5">
+      <c r="D445" s="51" t="s">
         <v>767</v>
       </c>
     </row>
@@ -10138,22 +11449,22 @@
       <c r="C447" t="s">
         <v>768</v>
       </c>
-      <c r="D447" s="62" t="s">
+      <c r="D447" s="47" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="448" spans="3:4" ht="16">
-      <c r="D448" s="62" t="s">
+      <c r="D448" s="47" t="s">
         <v>770</v>
       </c>
     </row>
     <row r="449" spans="3:4" ht="16">
-      <c r="D449" s="62" t="s">
+      <c r="D449" s="47" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="451" spans="3:4" ht="26.5">
-      <c r="D451" s="71" t="s">
+    <row r="451" spans="3:4" ht="52.5">
+      <c r="D451" s="52" t="s">
         <v>772</v>
       </c>
     </row>
@@ -10161,164 +11472,164 @@
       <c r="C453" t="s">
         <v>773</v>
       </c>
-      <c r="D453" s="72" t="s">
+      <c r="D453" s="96" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="454" spans="3:4" ht="16">
-      <c r="D454" s="72" t="s">
+    <row r="454" spans="3:4" ht="32">
+      <c r="D454" s="96" t="s">
         <v>775</v>
       </c>
     </row>
     <row r="455" spans="3:4" ht="16">
-      <c r="D455" s="72" t="s">
+      <c r="D455" s="96" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="457" spans="3:4" ht="39.5">
-      <c r="D457" s="70" t="s">
+    <row r="457" spans="3:4" ht="65.5">
+      <c r="D457" s="51" t="s">
         <v>777</v>
       </c>
     </row>
     <row r="459" spans="3:4">
-      <c r="D459" t="s">
+      <c r="D459" s="31" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="460" spans="3:4">
-      <c r="D460" s="73" t="s">
+      <c r="D460" s="97" t="s">
         <v>778</v>
       </c>
     </row>
     <row r="461" spans="3:4">
-      <c r="D461" s="73" t="s">
+      <c r="D461" s="97" t="s">
         <v>779</v>
       </c>
     </row>
     <row r="462" spans="3:4">
-      <c r="D462" s="73" t="s">
+      <c r="D462" s="97" t="s">
         <v>780</v>
       </c>
     </row>
     <row r="463" spans="3:4">
-      <c r="D463" s="73" t="s">
+      <c r="D463" s="97" t="s">
         <v>781</v>
       </c>
     </row>
     <row r="464" spans="3:4">
-      <c r="D464" s="73" t="s">
+      <c r="D464" s="97" t="s">
         <v>782</v>
       </c>
     </row>
     <row r="467" spans="2:4" ht="20.5" customHeight="1">
-      <c r="B467" s="74" t="s">
+      <c r="B467" s="53" t="s">
         <v>784</v>
       </c>
-      <c r="C467" s="74" t="s">
+      <c r="C467" s="53" t="s">
         <v>785</v>
       </c>
-      <c r="D467" s="74" t="s">
+      <c r="D467" s="53" t="s">
         <v>786</v>
       </c>
     </row>
     <row r="468" spans="2:4">
-      <c r="B468" s="76" t="s">
+      <c r="B468" s="55" t="s">
         <v>744</v>
       </c>
-      <c r="C468" s="75" t="s">
+      <c r="C468" s="54" t="s">
         <v>787</v>
       </c>
-      <c r="D468" s="75" t="s">
+      <c r="D468" s="54" t="s">
         <v>788</v>
       </c>
     </row>
     <row r="469" spans="2:4">
-      <c r="B469" s="76" t="s">
+      <c r="B469" s="55" t="s">
         <v>745</v>
       </c>
-      <c r="C469" s="75" t="s">
+      <c r="C469" s="54" t="s">
         <v>789</v>
       </c>
-      <c r="D469" s="75" t="s">
+      <c r="D469" s="54" t="s">
         <v>790</v>
       </c>
     </row>
     <row r="470" spans="2:4" ht="29">
-      <c r="B470" s="76" t="s">
+      <c r="B470" s="55" t="s">
         <v>747</v>
       </c>
-      <c r="C470" s="75" t="s">
+      <c r="C470" s="54" t="s">
         <v>791</v>
       </c>
-      <c r="D470" s="75" t="s">
+      <c r="D470" s="54" t="s">
         <v>792</v>
       </c>
     </row>
     <row r="471" spans="2:4">
-      <c r="B471" s="76" t="s">
+      <c r="B471" s="55" t="s">
         <v>746</v>
       </c>
-      <c r="C471" s="75" t="s">
+      <c r="C471" s="54" t="s">
         <v>793</v>
       </c>
-      <c r="D471" s="75" t="s">
+      <c r="D471" s="54" t="s">
         <v>794</v>
       </c>
     </row>
     <row r="472" spans="2:4" ht="29">
-      <c r="B472" s="76" t="s">
+      <c r="B472" s="55" t="s">
         <v>748</v>
       </c>
-      <c r="C472" s="75" t="s">
+      <c r="C472" s="54" t="s">
         <v>795</v>
       </c>
-      <c r="D472" s="75" t="s">
+      <c r="D472" s="54" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="476" spans="2:4" ht="16">
+    <row r="476" spans="2:4" ht="32">
       <c r="B476">
         <v>69</v>
       </c>
       <c r="C476" t="s">
         <v>798</v>
       </c>
-      <c r="D476" s="77" t="s">
+      <c r="D476" s="98" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="477" spans="2:4">
-      <c r="D477" t="s">
+      <c r="D477" s="31" t="s">
         <v>800</v>
       </c>
     </row>
     <row r="478" spans="2:4">
-      <c r="D478" s="57" t="s">
+      <c r="D478" s="90" t="s">
         <v>801</v>
       </c>
     </row>
     <row r="479" spans="2:4">
-      <c r="D479" s="57" t="s">
+      <c r="D479" s="90" t="s">
         <v>802</v>
       </c>
     </row>
     <row r="480" spans="2:4">
-      <c r="D480" s="57" t="s">
+      <c r="D480" s="90" t="s">
         <v>803</v>
       </c>
     </row>
     <row r="481" spans="2:4">
-      <c r="D481" s="57" t="s">
+      <c r="D481" s="90" t="s">
         <v>804</v>
       </c>
     </row>
     <row r="482" spans="2:4">
-      <c r="D482" s="57" t="s">
+      <c r="D482" s="90" t="s">
         <v>805</v>
       </c>
     </row>
     <row r="483" spans="2:4">
-      <c r="D483" s="57" t="s">
+      <c r="D483" s="90" t="s">
         <v>542</v>
       </c>
     </row>
@@ -10329,17 +11640,17 @@
       <c r="C485" t="s">
         <v>806</v>
       </c>
-      <c r="D485" s="77" t="s">
+      <c r="D485" s="98" t="s">
         <v>807</v>
       </c>
     </row>
     <row r="486" spans="2:4" ht="16">
-      <c r="D486" s="77" t="s">
+      <c r="D486" s="98" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="487" spans="2:4">
-      <c r="D487" t="s">
+    <row r="487" spans="2:4" ht="29">
+      <c r="D487" s="31" t="s">
         <v>812</v>
       </c>
     </row>
@@ -10347,15 +11658,15 @@
       <c r="B489">
         <v>71</v>
       </c>
-      <c r="C489" s="78" t="s">
+      <c r="C489" s="56" t="s">
         <v>809</v>
       </c>
-      <c r="D489" s="79" t="s">
+      <c r="D489" s="99" t="s">
         <v>810</v>
       </c>
     </row>
     <row r="490" spans="2:4">
-      <c r="D490" t="s">
+      <c r="D490" s="31" t="s">
         <v>811</v>
       </c>
     </row>
@@ -10366,155 +11677,155 @@
       <c r="C492" t="s">
         <v>813</v>
       </c>
-      <c r="D492" t="s">
+      <c r="D492" s="31" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="493" spans="2:4" ht="16">
-      <c r="B493" s="80"/>
-      <c r="C493" s="82" t="s">
+      <c r="B493" s="58"/>
+      <c r="C493" s="60" t="s">
         <v>814</v>
       </c>
-      <c r="D493" s="83" t="s">
+      <c r="D493" s="61" t="s">
         <v>815</v>
       </c>
     </row>
     <row r="494" spans="2:4" ht="16">
-      <c r="B494" s="81"/>
-      <c r="C494" s="82" t="s">
+      <c r="B494" s="59"/>
+      <c r="C494" s="60" t="s">
         <v>816</v>
       </c>
-      <c r="D494" s="83" t="s">
+      <c r="D494" s="61" t="s">
         <v>817</v>
       </c>
     </row>
     <row r="495" spans="2:4" ht="16">
-      <c r="B495" s="81"/>
-      <c r="C495" s="82" t="s">
+      <c r="B495" s="59"/>
+      <c r="C495" s="60" t="s">
         <v>818</v>
       </c>
-      <c r="D495" s="83" t="s">
+      <c r="D495" s="61" t="s">
         <v>819</v>
       </c>
     </row>
     <row r="496" spans="2:4" ht="16">
-      <c r="B496" s="81"/>
-      <c r="C496" s="82" t="s">
+      <c r="B496" s="59"/>
+      <c r="C496" s="60" t="s">
         <v>820</v>
       </c>
-      <c r="D496" s="83" t="s">
+      <c r="D496" s="61" t="s">
         <v>821</v>
       </c>
     </row>
     <row r="497" spans="2:4" ht="16">
-      <c r="B497" s="81"/>
-      <c r="C497" s="82" t="s">
+      <c r="B497" s="59"/>
+      <c r="C497" s="60" t="s">
         <v>822</v>
       </c>
-      <c r="D497" s="83" t="s">
+      <c r="D497" s="61" t="s">
         <v>823</v>
       </c>
     </row>
     <row r="498" spans="2:4" ht="16">
-      <c r="B498" s="81"/>
-      <c r="C498" s="82" t="s">
+      <c r="B498" s="59"/>
+      <c r="C498" s="60" t="s">
         <v>824</v>
       </c>
-      <c r="D498" s="83" t="s">
+      <c r="D498" s="61" t="s">
         <v>825</v>
       </c>
     </row>
     <row r="501" spans="2:4">
-      <c r="D501" s="80" t="s">
+      <c r="D501" s="58" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="503" spans="2:4">
-      <c r="C503" s="84" t="s">
+      <c r="C503" s="62" t="s">
         <v>826</v>
       </c>
-      <c r="D503" s="85" t="s">
+      <c r="D503" s="63" t="s">
         <v>827</v>
       </c>
     </row>
     <row r="504" spans="2:4">
-      <c r="B504" s="81"/>
-      <c r="C504" s="84" t="s">
+      <c r="B504" s="59"/>
+      <c r="C504" s="62" t="s">
         <v>828</v>
       </c>
-      <c r="D504" s="85" t="s">
+      <c r="D504" s="63" t="s">
         <v>829</v>
       </c>
     </row>
     <row r="505" spans="2:4">
-      <c r="B505" s="81"/>
-      <c r="C505" s="84" t="s">
+      <c r="B505" s="59"/>
+      <c r="C505" s="62" t="s">
         <v>830</v>
       </c>
-      <c r="D505" s="85" t="s">
+      <c r="D505" s="63" t="s">
         <v>831</v>
       </c>
     </row>
     <row r="506" spans="2:4">
-      <c r="B506" s="81"/>
-      <c r="C506" s="84" t="s">
+      <c r="B506" s="59"/>
+      <c r="C506" s="62" t="s">
         <v>832</v>
       </c>
-      <c r="D506" s="85" t="s">
+      <c r="D506" s="63" t="s">
         <v>833</v>
       </c>
     </row>
     <row r="507" spans="2:4">
-      <c r="B507" s="81"/>
-      <c r="C507" s="84" t="s">
+      <c r="B507" s="59"/>
+      <c r="C507" s="62" t="s">
         <v>834</v>
       </c>
-      <c r="D507" s="85" t="s">
+      <c r="D507" s="63" t="s">
         <v>835</v>
       </c>
     </row>
     <row r="508" spans="2:4">
-      <c r="B508" s="81"/>
-      <c r="C508" s="84" t="s">
+      <c r="B508" s="59"/>
+      <c r="C508" s="62" t="s">
         <v>836</v>
       </c>
-      <c r="D508" s="85" t="s">
+      <c r="D508" s="63" t="s">
         <v>837</v>
       </c>
     </row>
     <row r="509" spans="2:4">
-      <c r="B509" s="81"/>
-      <c r="C509" s="84" t="s">
+      <c r="B509" s="59"/>
+      <c r="C509" s="62" t="s">
         <v>838</v>
       </c>
-      <c r="D509" s="85" t="s">
+      <c r="D509" s="63" t="s">
         <v>839</v>
       </c>
     </row>
     <row r="510" spans="2:4">
-      <c r="B510" s="81"/>
-      <c r="C510" s="84" t="s">
+      <c r="B510" s="59"/>
+      <c r="C510" s="62" t="s">
         <v>840</v>
       </c>
-      <c r="D510" s="85" t="s">
+      <c r="D510" s="63" t="s">
         <v>841</v>
       </c>
     </row>
     <row r="511" spans="2:4">
-      <c r="B511" s="81"/>
-      <c r="C511" s="84" t="s">
+      <c r="B511" s="59"/>
+      <c r="C511" s="62" t="s">
         <v>842</v>
       </c>
-      <c r="D511" s="85" t="s">
+      <c r="D511" s="63" t="s">
         <v>843</v>
       </c>
     </row>
     <row r="512" spans="2:4">
-      <c r="B512" s="81"/>
-      <c r="C512" s="84" t="s">
+      <c r="B512" s="59"/>
+      <c r="C512" s="62" t="s">
         <v>844</v>
       </c>
-      <c r="D512" s="85" t="s">
+      <c r="D512" s="63" t="s">
         <v>845</v>
       </c>
     </row>
@@ -10522,31 +11833,31 @@
       <c r="B515">
         <v>73</v>
       </c>
-      <c r="C515" s="86" t="s">
+      <c r="C515" s="64" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="516" spans="2:4">
+    <row r="516" spans="2:4" ht="29">
       <c r="C516" t="s">
         <v>847</v>
       </c>
-      <c r="D516" s="38" t="s">
+      <c r="D516" s="84" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="517" spans="2:4">
+    <row r="517" spans="2:4" ht="29">
       <c r="C517" t="s">
         <v>849</v>
       </c>
-      <c r="D517" t="s">
+      <c r="D517" s="31" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="518" spans="2:4">
+    <row r="518" spans="2:4" ht="29">
       <c r="C518" t="s">
         <v>850</v>
       </c>
-      <c r="D518" t="s">
+      <c r="D518" s="31" t="s">
         <v>851</v>
       </c>
     </row>
@@ -10557,163 +11868,163 @@
       <c r="C521" t="s">
         <v>853</v>
       </c>
-      <c r="D521" t="s">
+      <c r="D521" s="31" t="s">
         <v>854</v>
       </c>
     </row>
     <row r="523" spans="2:4">
-      <c r="D523" s="87" t="s">
+      <c r="D523" s="100" t="s">
         <v>855</v>
       </c>
     </row>
     <row r="524" spans="2:4">
-      <c r="D524" s="87" t="s">
+      <c r="D524" s="100" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="525" spans="2:4">
-      <c r="D525" s="87" t="s">
+      <c r="D525" s="100" t="s">
         <v>872</v>
       </c>
     </row>
     <row r="526" spans="2:4">
-      <c r="D526" s="87" t="s">
+      <c r="D526" s="100" t="s">
         <v>856</v>
       </c>
     </row>
     <row r="527" spans="2:4">
-      <c r="D527" s="87" t="s">
+      <c r="D527" s="100" t="s">
         <v>857</v>
       </c>
     </row>
     <row r="528" spans="2:4">
-      <c r="D528" s="87" t="s">
+      <c r="D528" s="100" t="s">
         <v>858</v>
       </c>
     </row>
     <row r="529" spans="4:4">
-      <c r="D529" s="87" t="s">
+      <c r="D529" s="100" t="s">
         <v>859</v>
       </c>
     </row>
     <row r="530" spans="4:4">
-      <c r="D530" s="87" t="s">
+      <c r="D530" s="100" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="531" spans="4:4">
-      <c r="D531" s="88"/>
+      <c r="D531" s="101"/>
     </row>
     <row r="532" spans="4:4">
-      <c r="D532" s="87" t="s">
+      <c r="D532" s="100" t="s">
         <v>860</v>
       </c>
     </row>
     <row r="533" spans="4:4">
-      <c r="D533" s="87" t="s">
+      <c r="D533" s="100" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="534" spans="4:4">
-      <c r="D534" s="87" t="s">
+      <c r="D534" s="100" t="s">
         <v>862</v>
       </c>
     </row>
     <row r="535" spans="4:4">
-      <c r="D535" s="87" t="s">
+      <c r="D535" s="100" t="s">
         <v>863</v>
       </c>
     </row>
     <row r="536" spans="4:4">
-      <c r="D536" s="87" t="s">
+      <c r="D536" s="100" t="s">
         <v>864</v>
       </c>
     </row>
     <row r="537" spans="4:4">
-      <c r="D537" s="87" t="s">
+      <c r="D537" s="100" t="s">
         <v>865</v>
       </c>
     </row>
     <row r="538" spans="4:4">
-      <c r="D538" s="87" t="s">
+      <c r="D538" s="100" t="s">
         <v>866</v>
       </c>
     </row>
     <row r="539" spans="4:4">
-      <c r="D539" s="87" t="s">
+      <c r="D539" s="100" t="s">
         <v>867</v>
       </c>
     </row>
     <row r="540" spans="4:4">
-      <c r="D540" s="87" t="s">
+      <c r="D540" s="100" t="s">
         <v>868</v>
       </c>
     </row>
     <row r="541" spans="4:4">
-      <c r="D541" s="87" t="s">
+      <c r="D541" s="100" t="s">
         <v>869</v>
       </c>
     </row>
     <row r="542" spans="4:4">
-      <c r="D542" s="87" t="s">
+      <c r="D542" s="100" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="543" spans="4:4">
-      <c r="D543" s="88"/>
+      <c r="D543" s="101"/>
     </row>
     <row r="544" spans="4:4">
-      <c r="D544" s="87" t="s">
+      <c r="D544" s="100" t="s">
         <v>870</v>
       </c>
     </row>
     <row r="545" spans="2:4">
-      <c r="D545" s="87" t="s">
+      <c r="D545" s="100" t="s">
         <v>871</v>
       </c>
     </row>
     <row r="546" spans="2:4">
-      <c r="D546" s="87" t="s">
+      <c r="D546" s="100" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="547" spans="2:4">
-      <c r="D547" s="87" t="s">
+      <c r="D547" s="100" t="s">
         <v>873</v>
       </c>
     </row>
     <row r="548" spans="2:4">
-      <c r="D548" s="87" t="s">
+      <c r="D548" s="100" t="s">
         <v>874</v>
       </c>
     </row>
     <row r="549" spans="2:4">
-      <c r="D549" s="87" t="s">
+      <c r="D549" s="100" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="550" spans="2:4">
-      <c r="D550" s="87" t="s">
+      <c r="D550" s="100" t="s">
         <v>876</v>
       </c>
     </row>
     <row r="551" spans="2:4">
-      <c r="D551" s="87" t="s">
+      <c r="D551" s="100" t="s">
         <v>877</v>
       </c>
     </row>
     <row r="552" spans="2:4">
-      <c r="D552" s="87" t="s">
+      <c r="D552" s="100" t="s">
         <v>878</v>
       </c>
     </row>
     <row r="553" spans="2:4">
-      <c r="D553" s="87" t="s">
+      <c r="D553" s="100" t="s">
         <v>879</v>
       </c>
     </row>
     <row r="554" spans="2:4">
-      <c r="D554" s="87" t="s">
+      <c r="D554" s="100" t="s">
         <v>880</v>
       </c>
     </row>
@@ -10724,304 +12035,304 @@
       <c r="C556" t="s">
         <v>881</v>
       </c>
-      <c r="D556" s="89" t="s">
+      <c r="D556" s="102" t="s">
         <v>882</v>
       </c>
     </row>
     <row r="557" spans="2:4">
-      <c r="D557" s="43"/>
+      <c r="D557" s="103"/>
     </row>
     <row r="558" spans="2:4">
-      <c r="D558" s="91" t="s">
+      <c r="D558" s="104" t="s">
         <v>855</v>
       </c>
     </row>
     <row r="559" spans="2:4">
-      <c r="D559" s="91" t="s">
+      <c r="D559" s="104" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="560" spans="2:4">
-      <c r="D560" s="91" t="s">
+      <c r="D560" s="104" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="561" spans="4:4">
-      <c r="D561" s="91" t="s">
+      <c r="D561" s="104" t="s">
         <v>872</v>
       </c>
     </row>
     <row r="562" spans="4:4">
-      <c r="D562" s="91" t="s">
+      <c r="D562" s="104" t="s">
         <v>883</v>
       </c>
     </row>
     <row r="563" spans="4:4">
-      <c r="D563" s="91" t="s">
+      <c r="D563" s="104" t="s">
         <v>884</v>
       </c>
     </row>
     <row r="564" spans="4:4">
-      <c r="D564" s="91" t="s">
+      <c r="D564" s="104" t="s">
         <v>885</v>
       </c>
     </row>
     <row r="565" spans="4:4">
-      <c r="D565" s="91" t="s">
+      <c r="D565" s="104" t="s">
         <v>886</v>
       </c>
     </row>
     <row r="566" spans="4:4">
-      <c r="D566" s="91" t="s">
+      <c r="D566" s="104" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="567" spans="4:4">
-      <c r="D567" s="91" t="s">
+      <c r="D567" s="104" t="s">
         <v>888</v>
       </c>
     </row>
     <row r="568" spans="4:4">
-      <c r="D568" s="91" t="s">
+      <c r="D568" s="104" t="s">
         <v>889</v>
       </c>
     </row>
     <row r="569" spans="4:4">
-      <c r="D569" s="91" t="s">
+      <c r="D569" s="104" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="570" spans="4:4">
-      <c r="D570" s="90"/>
+      <c r="D570" s="105"/>
     </row>
     <row r="571" spans="4:4">
-      <c r="D571" s="91" t="s">
+      <c r="D571" s="104" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="572" spans="4:4">
-      <c r="D572" s="91" t="s">
+      <c r="D572" s="104" t="s">
         <v>857</v>
       </c>
     </row>
     <row r="573" spans="4:4">
-      <c r="D573" s="91" t="s">
+      <c r="D573" s="104" t="s">
         <v>858</v>
       </c>
     </row>
     <row r="574" spans="4:4">
-      <c r="D574" s="91" t="s">
+      <c r="D574" s="104" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="575" spans="4:4">
-      <c r="D575" s="90"/>
+      <c r="D575" s="105"/>
     </row>
     <row r="576" spans="4:4">
-      <c r="D576" s="91" t="s">
+      <c r="D576" s="104" t="s">
         <v>891</v>
       </c>
     </row>
     <row r="577" spans="4:4">
-      <c r="D577" s="91" t="s">
+      <c r="D577" s="104" t="s">
         <v>892</v>
       </c>
     </row>
     <row r="578" spans="4:4">
-      <c r="D578" s="91" t="s">
+      <c r="D578" s="104" t="s">
         <v>868</v>
       </c>
     </row>
     <row r="579" spans="4:4">
-      <c r="D579" s="91" t="s">
+      <c r="D579" s="104" t="s">
         <v>893</v>
       </c>
     </row>
     <row r="580" spans="4:4">
-      <c r="D580" s="91" t="s">
+      <c r="D580" s="104" t="s">
         <v>894</v>
       </c>
     </row>
     <row r="581" spans="4:4">
-      <c r="D581" s="91" t="s">
+      <c r="D581" s="104" t="s">
         <v>895</v>
       </c>
     </row>
     <row r="582" spans="4:4">
-      <c r="D582" s="91" t="s">
+      <c r="D582" s="104" t="s">
         <v>869</v>
       </c>
     </row>
     <row r="583" spans="4:4">
-      <c r="D583" s="91" t="s">
+      <c r="D583" s="104" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="584" spans="4:4">
-      <c r="D584" s="90"/>
+      <c r="D584" s="105"/>
     </row>
     <row r="585" spans="4:4">
-      <c r="D585" s="91" t="s">
+      <c r="D585" s="104" t="s">
         <v>896</v>
       </c>
     </row>
     <row r="586" spans="4:4">
-      <c r="D586" s="91" t="s">
+      <c r="D586" s="104" t="s">
         <v>897</v>
       </c>
     </row>
     <row r="587" spans="4:4">
-      <c r="D587" s="91" t="s">
+      <c r="D587" s="104" t="s">
         <v>898</v>
       </c>
     </row>
     <row r="588" spans="4:4">
-      <c r="D588" s="91" t="s">
+      <c r="D588" s="104" t="s">
         <v>899</v>
       </c>
     </row>
     <row r="589" spans="4:4">
-      <c r="D589" s="91" t="s">
+      <c r="D589" s="104" t="s">
         <v>900</v>
       </c>
     </row>
     <row r="590" spans="4:4">
-      <c r="D590" s="91" t="s">
+      <c r="D590" s="104" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="591" spans="4:4">
-      <c r="D591" s="90"/>
-    </row>
-    <row r="592" spans="4:4">
-      <c r="D592" s="91" t="s">
+      <c r="D591" s="105"/>
+    </row>
+    <row r="592" spans="4:4" ht="29">
+      <c r="D592" s="104" t="s">
         <v>901</v>
       </c>
     </row>
     <row r="593" spans="4:4">
-      <c r="D593" s="90"/>
+      <c r="D593" s="105"/>
     </row>
     <row r="594" spans="4:4">
-      <c r="D594" s="91" t="s">
+      <c r="D594" s="104" t="s">
         <v>902</v>
       </c>
     </row>
     <row r="595" spans="4:4">
-      <c r="D595" s="91" t="s">
+      <c r="D595" s="104" t="s">
         <v>900</v>
       </c>
     </row>
     <row r="596" spans="4:4">
-      <c r="D596" s="91" t="s">
+      <c r="D596" s="104" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="597" spans="4:4">
-      <c r="D597" s="90"/>
+      <c r="D597" s="105"/>
     </row>
     <row r="598" spans="4:4">
-      <c r="D598" s="91" t="s">
+      <c r="D598" s="104" t="s">
         <v>903</v>
       </c>
     </row>
     <row r="599" spans="4:4">
-      <c r="D599" s="91" t="s">
+      <c r="D599" s="104" t="s">
         <v>904</v>
       </c>
     </row>
     <row r="600" spans="4:4">
-      <c r="D600" s="91" t="s">
+      <c r="D600" s="104" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="601" spans="4:4">
-      <c r="D601" s="91" t="s">
+      <c r="D601" s="104" t="s">
         <v>873</v>
       </c>
     </row>
     <row r="602" spans="4:4">
-      <c r="D602" s="91" t="s">
+      <c r="D602" s="104" t="s">
         <v>905</v>
       </c>
     </row>
     <row r="603" spans="4:4">
-      <c r="D603" s="91" t="s">
+      <c r="D603" s="104" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="604" spans="4:4">
-      <c r="D604" s="91" t="s">
+      <c r="D604" s="104" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="605" spans="4:4">
-      <c r="D605" s="91" t="s">
+    <row r="605" spans="4:4" ht="29">
+      <c r="D605" s="104" t="s">
         <v>907</v>
       </c>
     </row>
     <row r="606" spans="4:4">
-      <c r="D606" s="91" t="s">
+      <c r="D606" s="104" t="s">
         <v>908</v>
       </c>
     </row>
     <row r="607" spans="4:4">
-      <c r="D607" s="91" t="s">
+      <c r="D607" s="104" t="s">
         <v>909</v>
       </c>
     </row>
     <row r="608" spans="4:4">
-      <c r="D608" s="91" t="s">
+      <c r="D608" s="104" t="s">
         <v>910</v>
       </c>
     </row>
     <row r="609" spans="2:4">
-      <c r="D609" s="91" t="s">
+      <c r="D609" s="104" t="s">
         <v>911</v>
       </c>
     </row>
     <row r="610" spans="2:4">
-      <c r="D610" s="91" t="s">
+      <c r="D610" s="104" t="s">
         <v>912</v>
       </c>
     </row>
     <row r="611" spans="2:4">
-      <c r="D611" s="91" t="s">
+      <c r="D611" s="104" t="s">
         <v>913</v>
       </c>
     </row>
     <row r="612" spans="2:4">
-      <c r="D612" s="91" t="s">
+      <c r="D612" s="104" t="s">
         <v>914</v>
       </c>
     </row>
     <row r="613" spans="2:4">
-      <c r="D613" s="91" t="s">
+      <c r="D613" s="104" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="614" spans="2:4">
-      <c r="D614" s="91" t="s">
+    <row r="614" spans="2:4" ht="29">
+      <c r="D614" s="104" t="s">
         <v>915</v>
       </c>
     </row>
     <row r="615" spans="2:4">
-      <c r="D615" s="91" t="s">
+      <c r="D615" s="104" t="s">
         <v>879</v>
       </c>
     </row>
     <row r="616" spans="2:4">
-      <c r="D616" s="91" t="s">
+      <c r="D616" s="104" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="620" spans="2:4" ht="16">
+    <row r="620" spans="2:4" ht="30">
       <c r="B620">
         <v>76</v>
       </c>
-      <c r="C620" s="79" t="s">
+      <c r="C620" s="57" t="s">
         <v>937</v>
       </c>
-      <c r="D620" t="s">
+      <c r="D620" s="31" t="s">
         <v>961</v>
       </c>
     </row>
@@ -11029,7 +12340,7 @@
       <c r="B621">
         <v>77</v>
       </c>
-      <c r="C621" s="92" t="s">
+      <c r="C621" s="65" t="s">
         <v>916</v>
       </c>
     </row>
@@ -11040,15 +12351,15 @@
       <c r="C622" t="s">
         <v>917</v>
       </c>
-      <c r="D622" s="93" t="s">
+      <c r="D622" s="66" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="624" spans="2:4" ht="16">
+    <row r="624" spans="2:4" ht="32">
       <c r="C624" t="s">
         <v>919</v>
       </c>
-      <c r="D624" s="79" t="s">
+      <c r="D624" s="99" t="s">
         <v>920</v>
       </c>
     </row>
@@ -11056,15 +12367,15 @@
       <c r="C625" t="s">
         <v>921</v>
       </c>
-      <c r="D625" s="79" t="s">
+      <c r="D625" s="99" t="s">
         <v>922</v>
       </c>
     </row>
-    <row r="626" spans="2:4" ht="16">
+    <row r="626" spans="2:4" ht="32">
       <c r="C626" t="s">
         <v>923</v>
       </c>
-      <c r="D626" s="79" t="s">
+      <c r="D626" s="99" t="s">
         <v>931</v>
       </c>
     </row>
@@ -11072,7 +12383,7 @@
       <c r="C627" t="s">
         <v>924</v>
       </c>
-      <c r="D627" s="79" t="s">
+      <c r="D627" s="99" t="s">
         <v>932</v>
       </c>
     </row>
@@ -11080,23 +12391,23 @@
       <c r="C628" t="s">
         <v>925</v>
       </c>
-      <c r="D628" s="79" t="s">
+      <c r="D628" s="99" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="629" spans="2:4" ht="16">
+    <row r="629" spans="2:4" ht="32">
       <c r="C629" t="s">
         <v>926</v>
       </c>
-      <c r="D629" s="79" t="s">
+      <c r="D629" s="99" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="630" spans="2:4" ht="16">
+    <row r="630" spans="2:4" ht="32">
       <c r="C630" t="s">
         <v>927</v>
       </c>
-      <c r="D630" s="79" t="s">
+      <c r="D630" s="99" t="s">
         <v>935</v>
       </c>
     </row>
@@ -11104,18 +12415,18 @@
       <c r="C631" t="s">
         <v>928</v>
       </c>
-      <c r="D631" s="79" t="s">
+      <c r="D631" s="99" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="633" spans="2:4">
+    <row r="633" spans="2:4" ht="29">
       <c r="B633">
         <v>79</v>
       </c>
       <c r="C633" t="s">
         <v>929</v>
       </c>
-      <c r="D633" t="s">
+      <c r="D633" s="31" t="s">
         <v>930</v>
       </c>
     </row>
@@ -11126,165 +12437,165 @@
       <c r="C635" t="s">
         <v>956</v>
       </c>
-      <c r="D635" s="57" t="s">
+      <c r="D635" s="90" t="s">
         <v>872</v>
       </c>
     </row>
     <row r="636" spans="2:4">
-      <c r="D636" s="57" t="s">
+      <c r="D636" s="90" t="s">
         <v>938</v>
       </c>
     </row>
     <row r="637" spans="2:4">
-      <c r="D637" s="57" t="s">
+      <c r="D637" s="90" t="s">
         <v>865</v>
       </c>
     </row>
     <row r="638" spans="2:4">
-      <c r="D638" s="57" t="s">
+      <c r="D638" s="90" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="639" spans="2:4">
-      <c r="D639" s="57"/>
+      <c r="D639" s="90"/>
     </row>
     <row r="640" spans="2:4">
-      <c r="D640" s="57" t="s">
+      <c r="D640" s="90" t="s">
         <v>940</v>
       </c>
     </row>
     <row r="641" spans="4:4">
-      <c r="D641" s="57" t="s">
+      <c r="D641" s="90" t="s">
         <v>941</v>
       </c>
     </row>
     <row r="642" spans="4:4">
-      <c r="D642" s="57" t="s">
+      <c r="D642" s="90" t="s">
         <v>942</v>
       </c>
     </row>
     <row r="643" spans="4:4">
-      <c r="D643" s="57" t="s">
+      <c r="D643" s="90" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="644" spans="4:4">
-      <c r="D644" s="57"/>
+      <c r="D644" s="90"/>
     </row>
     <row r="645" spans="4:4">
-      <c r="D645" s="57" t="s">
+      <c r="D645" s="90" t="s">
         <v>943</v>
       </c>
     </row>
     <row r="646" spans="4:4">
-      <c r="D646" s="57" t="s">
+      <c r="D646" s="90" t="s">
         <v>941</v>
       </c>
     </row>
     <row r="647" spans="4:4">
-      <c r="D647" s="57" t="s">
+      <c r="D647" s="90" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="648" spans="4:4">
-      <c r="D648" s="57" t="s">
+      <c r="D648" s="90" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="649" spans="4:4">
-      <c r="D649" s="57"/>
+      <c r="D649" s="90"/>
     </row>
     <row r="650" spans="4:4">
-      <c r="D650" s="57" t="s">
+      <c r="D650" s="90" t="s">
         <v>945</v>
       </c>
     </row>
     <row r="651" spans="4:4">
-      <c r="D651" s="57" t="s">
+      <c r="D651" s="90" t="s">
         <v>941</v>
       </c>
     </row>
     <row r="652" spans="4:4">
-      <c r="D652" s="57" t="s">
+      <c r="D652" s="90" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="653" spans="4:4">
-      <c r="D653" s="57" t="s">
+      <c r="D653" s="90" t="s">
         <v>947</v>
       </c>
     </row>
     <row r="654" spans="4:4">
-      <c r="D654" s="57" t="s">
+      <c r="D654" s="90" t="s">
         <v>948</v>
       </c>
     </row>
     <row r="655" spans="4:4">
-      <c r="D655" s="57" t="s">
+      <c r="D655" s="90" t="s">
         <v>949</v>
       </c>
     </row>
     <row r="656" spans="4:4">
-      <c r="D656" s="57" t="s">
+      <c r="D656" s="90" t="s">
         <v>950</v>
       </c>
     </row>
     <row r="657" spans="2:4">
-      <c r="D657" s="57" t="s">
+      <c r="D657" s="90" t="s">
         <v>951</v>
       </c>
     </row>
     <row r="658" spans="2:4">
-      <c r="D658" s="57" t="s">
+      <c r="D658" s="90" t="s">
         <v>952</v>
       </c>
     </row>
     <row r="659" spans="2:4">
-      <c r="D659" s="57" t="s">
+      <c r="D659" s="90" t="s">
         <v>953</v>
       </c>
     </row>
     <row r="660" spans="2:4">
-      <c r="D660" s="57" t="s">
+      <c r="D660" s="90" t="s">
         <v>954</v>
       </c>
     </row>
     <row r="661" spans="2:4">
-      <c r="D661" s="57" t="s">
+      <c r="D661" s="90" t="s">
         <v>955</v>
       </c>
     </row>
     <row r="662" spans="2:4">
-      <c r="D662" s="57" t="s">
+      <c r="D662" s="90" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="663" spans="2:4">
-      <c r="D663" s="57" t="s">
+      <c r="D663" s="90" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="665" spans="2:4">
+    <row r="665" spans="2:4" ht="29">
       <c r="B665">
         <v>90</v>
       </c>
       <c r="C665" t="s">
         <v>957</v>
       </c>
-      <c r="D665" t="s">
+      <c r="D665" s="31" t="s">
         <v>958</v>
       </c>
     </row>
     <row r="667" spans="2:4">
-      <c r="D667" s="94" t="s">
+      <c r="D667" s="106" t="s">
         <v>959</v>
       </c>
     </row>
     <row r="668" spans="2:4">
-      <c r="D668" s="57"/>
+      <c r="D668" s="90"/>
     </row>
     <row r="669" spans="2:4">
-      <c r="D669" s="94" t="s">
+      <c r="D669" s="106" t="s">
         <v>960</v>
       </c>
     </row>
@@ -11297,205 +12608,205 @@
       </c>
     </row>
     <row r="672" spans="2:4">
-      <c r="D672" t="s">
+      <c r="D672" s="31" t="s">
         <v>963</v>
       </c>
     </row>
     <row r="673" spans="3:4">
-      <c r="C673" s="96"/>
+      <c r="C673" s="68"/>
     </row>
     <row r="674" spans="3:4">
-      <c r="C674" s="97" t="s">
+      <c r="C674" s="69" t="s">
         <v>971</v>
       </c>
-      <c r="D674" t="s">
+      <c r="D674" s="31" t="s">
         <v>964</v>
       </c>
     </row>
     <row r="675" spans="3:4">
-      <c r="C675" s="97" t="s">
+      <c r="C675" s="69" t="s">
         <v>972</v>
       </c>
-      <c r="D675" t="s">
+      <c r="D675" s="31" t="s">
         <v>965</v>
       </c>
     </row>
     <row r="676" spans="3:4">
-      <c r="C676" s="97" t="s">
+      <c r="C676" s="69" t="s">
         <v>973</v>
       </c>
-      <c r="D676" t="s">
+      <c r="D676" s="31" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="677" spans="3:4">
-      <c r="C677" s="97" t="s">
+      <c r="C677" s="69" t="s">
         <v>974</v>
       </c>
-      <c r="D677" t="s">
+      <c r="D677" s="31" t="s">
         <v>966</v>
       </c>
     </row>
     <row r="678" spans="3:4">
-      <c r="C678" s="97" t="s">
+      <c r="C678" s="69" t="s">
         <v>969</v>
       </c>
-      <c r="D678" t="s">
+      <c r="D678" s="31" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="679" spans="3:4">
-      <c r="C679" s="97" t="s">
+      <c r="C679" s="69" t="s">
         <v>967</v>
       </c>
-      <c r="D679" t="s">
+      <c r="D679" s="31" t="s">
         <v>968</v>
       </c>
     </row>
-    <row r="681" spans="3:4">
-      <c r="C681" s="95"/>
-      <c r="D681" s="97" t="s">
+    <row r="681" spans="3:4" ht="27">
+      <c r="C681" s="67"/>
+      <c r="D681" s="107" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="682" spans="3:4">
-      <c r="C682" s="95"/>
-      <c r="D682" s="97"/>
+      <c r="C682" s="67"/>
+      <c r="D682" s="107"/>
     </row>
     <row r="683" spans="3:4">
-      <c r="C683" s="97" t="s">
+      <c r="C683" s="69" t="s">
         <v>978</v>
       </c>
-      <c r="D683" t="s">
+      <c r="D683" s="31" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="684" spans="3:4">
-      <c r="C684" s="97" t="s">
+      <c r="C684" s="69" t="s">
         <v>980</v>
       </c>
-      <c r="D684" t="s">
+      <c r="D684" s="31" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="685" spans="3:4">
-      <c r="C685" s="97" t="s">
+      <c r="C685" s="69" t="s">
         <v>984</v>
       </c>
-      <c r="D685" t="s">
+      <c r="D685" s="31" t="s">
         <v>985</v>
       </c>
     </row>
     <row r="686" spans="3:4">
-      <c r="C686" s="97" t="s">
+      <c r="C686" s="69" t="s">
         <v>982</v>
       </c>
-      <c r="D686" t="s">
+      <c r="D686" s="31" t="s">
         <v>983</v>
       </c>
     </row>
     <row r="687" spans="3:4">
-      <c r="C687" s="97" t="s">
+      <c r="C687" s="69" t="s">
         <v>986</v>
       </c>
-      <c r="D687" t="s">
+      <c r="D687" s="31" t="s">
         <v>987</v>
       </c>
     </row>
     <row r="688" spans="3:4">
       <c r="C688" s="5"/>
-      <c r="D688" t="s">
+      <c r="D688" s="31" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="689" spans="2:4">
-      <c r="C689" s="95"/>
+      <c r="C689" s="67"/>
     </row>
     <row r="690" spans="2:4" ht="15">
       <c r="B690">
         <v>92</v>
       </c>
-      <c r="C690" s="98" t="s">
+      <c r="C690" s="70" t="s">
         <v>988</v>
       </c>
     </row>
     <row r="692" spans="2:4">
-      <c r="C692" s="97" t="s">
+      <c r="C692" s="69" t="s">
         <v>989</v>
       </c>
-      <c r="D692" t="s">
+      <c r="D692" s="31" t="s">
         <v>990</v>
       </c>
     </row>
     <row r="693" spans="2:4">
-      <c r="C693" s="97" t="s">
+      <c r="C693" s="69" t="s">
         <v>991</v>
       </c>
-      <c r="D693" t="s">
+      <c r="D693" s="31" t="s">
         <v>992</v>
       </c>
     </row>
     <row r="694" spans="2:4">
-      <c r="C694" s="97" t="s">
+      <c r="C694" s="69" t="s">
         <v>993</v>
       </c>
-      <c r="D694" t="s">
+      <c r="D694" s="31" t="s">
         <v>994</v>
       </c>
     </row>
     <row r="695" spans="2:4">
-      <c r="C695" s="97" t="s">
+      <c r="C695" s="69" t="s">
         <v>995</v>
       </c>
-      <c r="D695" t="s">
+      <c r="D695" s="31" t="s">
         <v>996</v>
       </c>
     </row>
     <row r="696" spans="2:4">
-      <c r="C696" s="97" t="s">
+      <c r="C696" s="69" t="s">
         <v>997</v>
       </c>
-      <c r="D696" t="s">
+      <c r="D696" s="31" t="s">
         <v>998</v>
       </c>
     </row>
     <row r="697" spans="2:4">
-      <c r="C697" s="97" t="s">
+      <c r="C697" s="69" t="s">
         <v>999</v>
       </c>
-      <c r="D697" t="s">
+      <c r="D697" s="31" t="s">
         <v>1000</v>
       </c>
     </row>
     <row r="698" spans="2:4">
-      <c r="C698" s="97" t="s">
+      <c r="C698" s="69" t="s">
         <v>1001</v>
       </c>
-      <c r="D698" t="s">
+      <c r="D698" s="31" t="s">
         <v>1002</v>
       </c>
     </row>
     <row r="699" spans="2:4">
-      <c r="C699" s="97" t="s">
+      <c r="C699" s="69" t="s">
         <v>1003</v>
       </c>
-      <c r="D699" t="s">
+      <c r="D699" s="31" t="s">
         <v>1004</v>
       </c>
     </row>
     <row r="700" spans="2:4">
-      <c r="C700" s="97" t="s">
+      <c r="C700" s="69" t="s">
         <v>1005</v>
       </c>
-      <c r="D700" t="s">
+      <c r="D700" s="31" t="s">
         <v>1006</v>
       </c>
     </row>
     <row r="701" spans="2:4">
-      <c r="C701" s="97" t="s">
+      <c r="C701" s="69" t="s">
         <v>1007</v>
       </c>
-      <c r="D701" t="s">
+      <c r="D701" s="31" t="s">
         <v>1008</v>
       </c>
     </row>
@@ -11503,121 +12814,121 @@
       <c r="B703">
         <v>93</v>
       </c>
-      <c r="C703" s="97" t="s">
-        <v>1011</v>
+      <c r="C703" s="69" t="s">
+        <v>1010</v>
       </c>
     </row>
     <row r="704" spans="2:4">
       <c r="B704">
         <v>94</v>
       </c>
-      <c r="C704" s="97" t="s">
+      <c r="C704" s="69" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D704" s="31" t="s">
         <v>1012</v>
       </c>
-      <c r="D704" t="s">
+    </row>
+    <row r="705" spans="2:4">
+      <c r="D705" s="31" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="705" spans="2:4">
-      <c r="D705" t="s">
+    <row r="706" spans="2:4" ht="29">
+      <c r="D706" s="31" t="s">
         <v>1014</v>
-      </c>
-    </row>
-    <row r="706" spans="2:4">
-      <c r="D706" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="708" spans="2:4">
       <c r="C708" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D708" s="31" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="709" spans="2:4">
+      <c r="D709" s="71" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="710" spans="2:4">
+      <c r="D710" s="71" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="711" spans="2:4">
+      <c r="D711" s="71" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="712" spans="2:4">
+      <c r="D712" s="71" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="713" spans="2:4">
+      <c r="D713" s="31" t="s">
         <v>1021</v>
       </c>
-      <c r="D708" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="709" spans="2:4">
-      <c r="D709" s="39" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="710" spans="2:4">
-      <c r="D710" s="39" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="711" spans="2:4">
-      <c r="D711" s="39" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="712" spans="2:4">
-      <c r="D712" s="39" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="713" spans="2:4">
-      <c r="D713" t="s">
+    </row>
+    <row r="714" spans="2:4">
+      <c r="D714" s="71" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="715" spans="2:4">
+      <c r="D715" s="71" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="714" spans="2:4">
-      <c r="D714" s="39" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="715" spans="2:4">
-      <c r="D715" s="39" t="s">
-        <v>1023</v>
-      </c>
-    </row>
     <row r="716" spans="2:4">
-      <c r="D716" s="39"/>
+      <c r="D716" s="71"/>
     </row>
     <row r="717" spans="2:4">
       <c r="B717">
         <v>95</v>
       </c>
       <c r="C717" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D717" s="86" t="s">
         <v>1025</v>
       </c>
-      <c r="D717" s="41" t="s">
+    </row>
+    <row r="718" spans="2:4">
+      <c r="D718" s="86" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="718" spans="2:4">
-      <c r="D718" s="41" t="s">
+    <row r="719" spans="2:4">
+      <c r="D719" s="86" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="719" spans="2:4">
-      <c r="D719" s="41" t="s">
+    <row r="720" spans="2:4" ht="29">
+      <c r="D720" s="86" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="720" spans="2:4">
-      <c r="D720" s="41" t="s">
+    <row r="721" spans="2:4">
+      <c r="D721" s="86" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="721" spans="2:4">
-      <c r="D721" s="41" t="s">
+    <row r="722" spans="2:4" ht="29">
+      <c r="D722" s="86" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="722" spans="2:4">
-      <c r="D722" s="41" t="s">
+    <row r="723" spans="2:4">
+      <c r="D723" s="86" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="723" spans="2:4">
-      <c r="D723" s="41" t="s">
+    <row r="724" spans="2:4">
+      <c r="D724" s="86" t="s">
         <v>1032</v>
-      </c>
-    </row>
-    <row r="724" spans="2:4">
-      <c r="D724" s="41" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="726" spans="2:4">
@@ -11625,40 +12936,505 @@
         <v>96</v>
       </c>
       <c r="C726" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D726" s="86" t="s">
         <v>1034</v>
       </c>
-      <c r="D726" s="41" t="s">
+    </row>
+    <row r="727" spans="2:4">
+      <c r="D727" s="86" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="727" spans="2:4">
-      <c r="D727" s="41" t="s">
+    <row r="728" spans="2:4">
+      <c r="D728" s="86" t="s">
         <v>1036</v>
       </c>
     </row>
-    <row r="728" spans="2:4">
-      <c r="D728" s="41" t="s">
+    <row r="729" spans="2:4">
+      <c r="D729" s="86" t="s">
         <v>1037</v>
       </c>
     </row>
-    <row r="729" spans="2:4">
-      <c r="D729" s="41" t="s">
+    <row r="730" spans="2:4">
+      <c r="D730" s="86" t="s">
         <v>1038</v>
       </c>
     </row>
-    <row r="730" spans="2:4">
-      <c r="D730" s="41" t="s">
+    <row r="731" spans="2:4">
+      <c r="D731" s="86" t="s">
         <v>1039</v>
       </c>
     </row>
-    <row r="731" spans="2:4">
-      <c r="D731" s="41" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="733" spans="2:4">
+    <row r="733" spans="2:4" ht="16">
       <c r="B733">
         <v>97</v>
+      </c>
+      <c r="C733" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D733" s="72" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="734" spans="2:4" ht="32">
+      <c r="D734" s="99" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="735" spans="2:4" ht="32">
+      <c r="D735" s="99" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="736" spans="2:4" ht="32">
+      <c r="D736" s="99" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="737" spans="2:5" ht="16">
+      <c r="D737" s="99" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="738" spans="2:5">
+      <c r="D738" s="108"/>
+    </row>
+    <row r="739" spans="2:5" ht="16">
+      <c r="D739" s="74" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="740" spans="2:5" ht="16">
+      <c r="D740" s="109" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="741" spans="2:5" ht="16">
+      <c r="D741" s="109" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="742" spans="2:5" ht="32">
+      <c r="D742" s="74" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="743" spans="2:5" ht="32">
+      <c r="D743" s="74" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="744" spans="2:5">
+      <c r="D744" s="108"/>
+    </row>
+    <row r="745" spans="2:5" ht="32">
+      <c r="B745">
+        <v>98</v>
+      </c>
+      <c r="C745" s="112" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D745" s="109" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="746" spans="2:5" ht="16">
+      <c r="D746" s="109" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="747" spans="2:5" ht="16">
+      <c r="D747" s="109" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="748" spans="2:5" ht="16">
+      <c r="D748" s="109" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="749" spans="2:5" ht="16">
+      <c r="D749" s="109" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="750" spans="2:5" ht="16">
+      <c r="D750" s="109" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="752" spans="2:5">
+      <c r="B752" s="73">
+        <v>99</v>
+      </c>
+      <c r="C752" s="73" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D752" s="108"/>
+      <c r="E752" s="73"/>
+    </row>
+    <row r="753" spans="2:5" ht="32" customHeight="1">
+      <c r="B753" s="73"/>
+      <c r="C753" s="75" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D753" s="75" t="s">
+        <v>688</v>
+      </c>
+      <c r="E753" s="75" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="754" spans="2:5" ht="42" customHeight="1">
+      <c r="B754" s="73"/>
+      <c r="C754" s="76" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D754" s="61"/>
+      <c r="E754" s="76" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="755" spans="2:5" ht="116" customHeight="1">
+      <c r="B755" s="73"/>
+      <c r="C755" s="76" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D755" s="61" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E755" s="76" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="756" spans="2:5" ht="71" customHeight="1">
+      <c r="B756" s="73"/>
+      <c r="C756" s="76" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D756" s="61" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E756" s="61" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="757" spans="2:5" ht="97" customHeight="1">
+      <c r="B757" s="73"/>
+      <c r="C757" s="76" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D757" s="61" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E757" s="76" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="758" spans="2:5" ht="42" customHeight="1">
+      <c r="B758" s="73"/>
+      <c r="C758" s="76" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D758" s="61" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E758" s="76" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="759" spans="2:5" ht="29" customHeight="1">
+      <c r="B759" s="73"/>
+      <c r="C759" s="76" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D759" s="61" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E759" s="76" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="760" spans="2:5" ht="29" customHeight="1">
+      <c r="B760" s="73"/>
+      <c r="C760" s="76" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D760" s="61" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E760" s="76" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="761" spans="2:5" ht="29" customHeight="1">
+      <c r="B761" s="73"/>
+      <c r="C761" s="76" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D761" s="61" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E761" s="76" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="762" spans="2:5" ht="16" customHeight="1">
+      <c r="B762" s="73"/>
+      <c r="C762" s="76" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D762" s="61" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E762" s="76" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="763" spans="2:5" ht="39" customHeight="1">
+      <c r="B763" s="73"/>
+      <c r="C763" s="76" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D763" s="61" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E763" s="76" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="764" spans="2:5" ht="74" customHeight="1">
+      <c r="B764" s="73"/>
+      <c r="C764" s="76" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D764" s="61" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E764" s="76" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="765" spans="2:5" ht="29" customHeight="1">
+      <c r="B765" s="73"/>
+      <c r="C765" s="76" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D765" s="61" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E765" s="76" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="766" spans="2:5" ht="80" customHeight="1">
+      <c r="B766" s="73"/>
+      <c r="C766" s="76" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D766" s="61" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E766" s="76" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="767" spans="2:5" ht="58" customHeight="1">
+      <c r="B767" s="73"/>
+      <c r="C767" s="76" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D767" s="61" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E767" s="61" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="768" spans="2:5" ht="132" customHeight="1">
+      <c r="B768" s="73"/>
+      <c r="C768" s="76" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D768" s="61" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E768" s="76" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="769" spans="2:5" ht="58" customHeight="1">
+      <c r="B769" s="73"/>
+      <c r="C769" s="76" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D769" s="61" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E769" s="61" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="770" spans="2:5" ht="26" customHeight="1">
+      <c r="B770" s="73"/>
+      <c r="C770" s="76" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D770" s="61" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E770" s="76" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="771" spans="2:5" ht="39" customHeight="1">
+      <c r="B771" s="73"/>
+      <c r="C771" s="76" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D771" s="61" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E771" s="76" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="772" spans="2:5" ht="26" customHeight="1">
+      <c r="B772" s="73"/>
+      <c r="C772" s="76" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D772" s="61" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E772" s="76" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="773" spans="2:5" ht="61" customHeight="1">
+      <c r="B773" s="73"/>
+      <c r="C773" s="76" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D773" s="61" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E773" s="76" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="774" spans="2:5" ht="45" customHeight="1">
+      <c r="B774" s="73"/>
+      <c r="C774" s="76" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D774" s="61" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E774" s="61" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="775" spans="2:5">
+      <c r="B775" s="73"/>
+      <c r="C775" s="73"/>
+      <c r="D775" s="108"/>
+      <c r="E775" s="73"/>
+    </row>
+    <row r="776" spans="2:5">
+      <c r="B776" s="73"/>
+      <c r="C776" s="73"/>
+      <c r="D776" s="108"/>
+      <c r="E776" s="73"/>
+    </row>
+    <row r="777" spans="2:5">
+      <c r="B777" s="73">
+        <v>100</v>
+      </c>
+      <c r="C777" s="110" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D777" s="108"/>
+      <c r="E777" s="73"/>
+    </row>
+    <row r="778" spans="2:5">
+      <c r="B778" s="73"/>
+      <c r="C778" s="73"/>
+      <c r="D778" s="108"/>
+      <c r="E778" s="73"/>
+    </row>
+    <row r="779" spans="2:5" ht="16">
+      <c r="B779" s="73"/>
+      <c r="C779" s="75" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D779" s="75" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E779" s="75" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="780" spans="2:5" ht="16">
+      <c r="B780" s="73"/>
+      <c r="C780" s="111" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D780" s="61" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E780" s="61" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="781" spans="2:5" ht="16">
+      <c r="B781" s="73"/>
+      <c r="C781" s="111" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D781" s="61" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E781" s="61" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="782" spans="2:5" ht="16">
+      <c r="B782" s="73"/>
+      <c r="C782" s="111" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D782" s="61" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E782" s="61" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="783" spans="2:5" ht="16">
+      <c r="B783" s="73"/>
+      <c r="C783" s="111" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D783" s="61" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E783" s="61" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="784" spans="2:5" ht="16">
+      <c r="B784" s="73"/>
+      <c r="C784" s="111" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D784" s="61" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E784" s="61" t="s">
+        <v>1138</v>
       </c>
     </row>
   </sheetData>
@@ -12081,7 +13857,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>1009</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="42" spans="2:5">
@@ -12453,7 +14229,7 @@
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="71" spans="2:5">
@@ -12812,36 +14588,36 @@
   </cols>
   <sheetData>
     <row r="7" spans="4:8">
-      <c r="E7" s="26"/>
+      <c r="E7" s="22"/>
     </row>
     <row r="8" spans="4:8" ht="15.5">
-      <c r="D8" s="27"/>
-      <c r="E8" s="28" t="s">
+      <c r="D8" s="23"/>
+      <c r="E8" s="24" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:8">
-      <c r="D9" s="22">
+      <c r="D9" s="18">
         <v>1</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="G9" s="30" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="10" spans="4:8">
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="19" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:8">
-      <c r="D11" s="22"/>
-      <c r="E11" s="23" t="s">
+      <c r="D11" s="18"/>
+      <c r="E11" s="19" t="s">
         <v>251</v>
       </c>
       <c r="G11" t="s">
@@ -12849,14 +14625,14 @@
       </c>
     </row>
     <row r="12" spans="4:8">
-      <c r="D12" s="22"/>
-      <c r="E12" s="23" t="s">
+      <c r="D12" s="18"/>
+      <c r="E12" s="19" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:8">
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
       <c r="F13">
         <v>1</v>
       </c>
@@ -12868,10 +14644,10 @@
       </c>
     </row>
     <row r="14" spans="4:8">
-      <c r="D14" s="22">
+      <c r="D14" s="18">
         <v>2</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="19" t="s">
         <v>253</v>
       </c>
       <c r="F14">
@@ -12885,10 +14661,10 @@
       </c>
     </row>
     <row r="15" spans="4:8">
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="19" t="s">
         <v>255</v>
       </c>
       <c r="H15" t="s">
@@ -12896,8 +14672,8 @@
       </c>
     </row>
     <row r="16" spans="4:8">
-      <c r="D16" s="22"/>
-      <c r="E16" s="23" t="s">
+      <c r="D16" s="18"/>
+      <c r="E16" s="19" t="s">
         <v>256</v>
       </c>
       <c r="F16">
@@ -12911,8 +14687,8 @@
       </c>
     </row>
     <row r="17" spans="3:8">
-      <c r="D17" s="22"/>
-      <c r="E17" s="23" t="s">
+      <c r="D17" s="18"/>
+      <c r="E17" s="19" t="s">
         <v>257</v>
       </c>
       <c r="F17">
@@ -12926,14 +14702,14 @@
       </c>
     </row>
     <row r="18" spans="3:8">
-      <c r="D18" s="22"/>
-      <c r="E18" s="23" t="s">
+      <c r="D18" s="18"/>
+      <c r="E18" s="19" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="19" spans="3:8">
-      <c r="D19" s="24"/>
-      <c r="E19" s="25" t="s">
+      <c r="D19" s="20"/>
+      <c r="E19" s="21" t="s">
         <v>259</v>
       </c>
     </row>
@@ -12977,7 +14753,7 @@
       <c r="D29" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="E29" s="29" t="s">
+      <c r="E29" s="25" t="s">
         <v>267</v>
       </c>
     </row>
@@ -13238,7 +15014,7 @@
       <c r="C54">
         <v>24</v>
       </c>
-      <c r="D54" s="35" t="s">
+      <c r="D54" s="31" t="s">
         <v>356</v>
       </c>
       <c r="E54" t="s">
@@ -13318,7 +15094,7 @@
       <c r="D61" t="s">
         <v>369</v>
       </c>
-      <c r="E61" s="36" t="s">
+      <c r="E61" s="32" t="s">
         <v>370</v>
       </c>
     </row>
@@ -13367,7 +15143,7 @@
       <c r="D66" t="s">
         <v>379</v>
       </c>
-      <c r="E66" s="36" t="s">
+      <c r="E66" s="32" t="s">
         <v>380</v>
       </c>
     </row>
@@ -13437,27 +15213,27 @@
       </c>
     </row>
     <row r="11" spans="3:7">
-      <c r="C11" s="20">
+      <c r="C11" s="16">
         <v>1</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18" t="s">
+      <c r="D11" s="14"/>
+      <c r="E11" s="14" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="12" spans="3:7">
-      <c r="C12" s="20">
+      <c r="C12" s="16">
         <v>2</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18" t="s">
+      <c r="D12" s="14"/>
+      <c r="E12" s="14" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="13" spans="3:7">
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18" t="s">
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14" t="s">
         <v>290</v>
       </c>
       <c r="G13" t="s">
@@ -13465,247 +15241,247 @@
       </c>
     </row>
     <row r="14" spans="3:7">
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18" t="s">
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="15" spans="3:7">
-      <c r="C15" s="20">
+      <c r="C15" s="16">
         <v>3</v>
       </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18" t="s">
+      <c r="D15" s="14"/>
+      <c r="E15" s="14" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="16" spans="3:7">
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="17" spans="3:5">
-      <c r="C17" s="20">
+      <c r="C17" s="16">
         <v>4</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18" t="s">
+      <c r="D17" s="14"/>
+      <c r="E17" s="14" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="18" spans="3:5">
-      <c r="C18" s="18"/>
-      <c r="D18" s="19" t="s">
+      <c r="C18" s="14"/>
+      <c r="D18" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="14" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="19" spans="3:5">
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18" t="s">
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="20" spans="3:5">
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18" t="s">
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="21" spans="3:5">
-      <c r="C21" s="20">
+      <c r="C21" s="16">
         <v>5</v>
       </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18" t="s">
+      <c r="D21" s="14"/>
+      <c r="E21" s="14" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="22" spans="3:5">
-      <c r="C22" s="18"/>
-      <c r="D22" s="19" t="s">
+      <c r="C22" s="14"/>
+      <c r="D22" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="14" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="23" spans="3:5">
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18" t="s">
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="24" spans="3:5">
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18" t="s">
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="25" spans="3:5">
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18" t="s">
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="26" spans="3:5">
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18" t="s">
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="27" spans="3:5">
-      <c r="C27" s="18"/>
-      <c r="D27" s="19" t="s">
+      <c r="C27" s="14"/>
+      <c r="D27" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="14" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="28" spans="3:5">
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18" t="s">
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="29" spans="3:5">
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18" t="s">
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="30" spans="3:5">
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18" t="s">
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="31" spans="3:5">
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18" t="s">
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="32" spans="3:5">
-      <c r="C32" s="18"/>
-      <c r="D32" s="19" t="s">
+      <c r="C32" s="14"/>
+      <c r="D32" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="14" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="33" spans="3:5">
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18" t="s">
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="34" spans="3:5">
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18" t="s">
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="35" spans="3:5">
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18" t="s">
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="36" spans="3:5">
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18" t="s">
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="37" spans="3:5">
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18" t="s">
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18" t="s">
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="39" spans="3:5" ht="15.5">
-      <c r="C39" s="19">
+      <c r="C39" s="15">
         <v>6</v>
       </c>
-      <c r="D39" s="21" t="s">
+      <c r="D39" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="E39" s="21" t="s">
+      <c r="E39" s="17" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="40" spans="3:5">
-      <c r="C40" s="18"/>
-      <c r="D40" s="18" t="s">
+      <c r="C40" s="14"/>
+      <c r="D40" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="E40" s="14" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="41" spans="3:5">
-      <c r="C41" s="18"/>
-      <c r="D41" s="18" t="s">
+      <c r="C41" s="14"/>
+      <c r="D41" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="14" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="42" spans="3:5">
-      <c r="C42" s="18"/>
-      <c r="D42" s="18" t="s">
+      <c r="C42" s="14"/>
+      <c r="D42" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="14" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="43" spans="3:5">
-      <c r="C43" s="18"/>
-      <c r="D43" s="18" t="s">
+      <c r="C43" s="14"/>
+      <c r="D43" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="E43" s="18" t="s">
+      <c r="E43" s="14" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="44" spans="3:5">
-      <c r="C44" s="18"/>
-      <c r="D44" s="18" t="s">
+      <c r="C44" s="14"/>
+      <c r="D44" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="E44" s="18" t="s">
+      <c r="E44" s="14" t="s">
         <v>246</v>
       </c>
     </row>
@@ -13741,146 +15517,146 @@
       </c>
     </row>
     <row r="56" spans="4:5" ht="18.5">
-      <c r="D56" s="30"/>
-      <c r="E56" s="30" t="s">
+      <c r="D56" s="26"/>
+      <c r="E56" s="26" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="57" spans="4:5">
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
     </row>
     <row r="58" spans="4:5" ht="15.5">
-      <c r="D58" s="30">
+      <c r="D58" s="26">
         <v>1</v>
       </c>
-      <c r="E58" s="31" t="s">
+      <c r="E58" s="27" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="59" spans="4:5">
-      <c r="D59" s="30"/>
-      <c r="E59" s="32" t="s">
+      <c r="D59" s="26"/>
+      <c r="E59" s="28" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="60" spans="4:5">
-      <c r="D60" s="30"/>
-      <c r="E60" s="32"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="28"/>
     </row>
     <row r="61" spans="4:5">
-      <c r="D61" s="30">
+      <c r="D61" s="26">
         <v>2</v>
       </c>
-      <c r="E61" s="33" t="s">
+      <c r="E61" s="29" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="62" spans="4:5">
-      <c r="D62" s="30"/>
-      <c r="E62" s="30" t="s">
+      <c r="D62" s="26"/>
+      <c r="E62" s="26" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="63" spans="4:5">
-      <c r="D63" s="30"/>
-      <c r="E63" s="30" t="s">
+      <c r="D63" s="26"/>
+      <c r="E63" s="26" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="64" spans="4:5">
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
     </row>
     <row r="65" spans="4:5">
-      <c r="D65" s="30">
+      <c r="D65" s="26">
         <v>3</v>
       </c>
-      <c r="E65" s="33" t="s">
+      <c r="E65" s="29" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="66" spans="4:5">
-      <c r="D66" s="30"/>
-      <c r="E66" s="30" t="s">
+      <c r="D66" s="26"/>
+      <c r="E66" s="26" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="67" spans="4:5">
-      <c r="D67" s="30"/>
-      <c r="E67" s="30" t="s">
+      <c r="D67" s="26"/>
+      <c r="E67" s="26" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="68" spans="4:5">
-      <c r="D68" s="30"/>
-      <c r="E68" s="30"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
     </row>
     <row r="69" spans="4:5">
-      <c r="D69" s="30">
+      <c r="D69" s="26">
         <v>4</v>
       </c>
-      <c r="E69" s="33" t="s">
+      <c r="E69" s="29" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="70" spans="4:5">
-      <c r="D70" s="30"/>
-      <c r="E70" s="30" t="s">
+      <c r="D70" s="26"/>
+      <c r="E70" s="26" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="71" spans="4:5">
-      <c r="D71" s="30"/>
-      <c r="E71" s="30" t="s">
+      <c r="D71" s="26"/>
+      <c r="E71" s="26" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="72" spans="4:5">
-      <c r="D72" s="30"/>
-      <c r="E72" s="30"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
     </row>
     <row r="73" spans="4:5">
-      <c r="D73" s="30">
+      <c r="D73" s="26">
         <v>5</v>
       </c>
-      <c r="E73" s="33" t="s">
+      <c r="E73" s="29" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="74" spans="4:5">
-      <c r="D74" s="30"/>
-      <c r="E74" s="30" t="s">
+      <c r="D74" s="26"/>
+      <c r="E74" s="26" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="75" spans="4:5">
-      <c r="D75" s="30"/>
-      <c r="E75" s="30" t="s">
+      <c r="D75" s="26"/>
+      <c r="E75" s="26" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="76" spans="4:5">
-      <c r="D76" s="30"/>
-      <c r="E76" s="30"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
     </row>
     <row r="77" spans="4:5">
-      <c r="D77" s="30">
+      <c r="D77" s="26">
         <v>6</v>
       </c>
-      <c r="E77" s="33" t="s">
+      <c r="E77" s="29" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="78" spans="4:5">
-      <c r="D78" s="30"/>
-      <c r="E78" s="30" t="s">
+      <c r="D78" s="26"/>
+      <c r="E78" s="26" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="79" spans="4:5">
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/NOTES.xlsx
+++ b/doc/NOTES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MY PC\Documents\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58E4391-A11F-418F-8836-F764ED230D4E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{120D26E5-AB73-4254-92DE-A8C2FDDA3038}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="1139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="1163">
   <si>
     <t>HTML</t>
   </si>
@@ -7543,6 +7543,98 @@
   </si>
   <si>
     <t>Slightly Harder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diff. b/w grid properties </t>
+  </si>
+  <si>
+    <t>Applies To</t>
+  </si>
+  <si>
+    <t>Defines</t>
+  </si>
+  <si>
+    <t>Explicit / Implicit</t>
+  </si>
+  <si>
+    <t>Example Use</t>
+  </si>
+  <si>
+    <t>Container</t>
+  </si>
+  <si>
+    <t>Row sizes</t>
+  </si>
+  <si>
+    <t>Explicit</t>
+  </si>
+  <si>
+    <t>100px 1fr</t>
+  </si>
+  <si>
+    <t>Column sizes</t>
+  </si>
+  <si>
+    <t>1fr 2fr</t>
+  </si>
+  <si>
+    <t>Named layout pattern</t>
+  </si>
+  <si>
+    <t>"a b"</t>
+  </si>
+  <si>
+    <r>
+      <t>grid-row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>grid-column</t>
+    </r>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Start/end lines of placement</t>
+  </si>
+  <si>
+    <t>Manual (item-level)</t>
+  </si>
+  <si>
+    <t>Size of implicit rows</t>
+  </si>
+  <si>
+    <t>Implicit</t>
+  </si>
+  <si>
+    <t>Size of implicit columns</t>
+  </si>
+  <si>
+    <t>150px</t>
+  </si>
+  <si>
+    <t>Auto-placement direction</t>
+  </si>
+  <si>
+    <t>Auto behavior</t>
+  </si>
+  <si>
+    <t>row dense</t>
   </si>
 </sst>
 </file>
@@ -8045,7 +8137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8319,6 +8411,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9072,7 +9170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B8:E784"/>
+  <dimension ref="B8:G796"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="29.81640625" customWidth="1"/>
@@ -13029,7 +13127,7 @@
     <row r="744" spans="2:5">
       <c r="D744" s="108"/>
     </row>
-    <row r="745" spans="2:5" ht="32">
+    <row r="745" spans="2:5" ht="16">
       <c r="B745">
         <v>98</v>
       </c>
@@ -13435,6 +13533,150 @@
       </c>
       <c r="E784" s="61" t="s">
         <v>1138</v>
+      </c>
+    </row>
+    <row r="787" spans="2:7" ht="16">
+      <c r="B787">
+        <v>101</v>
+      </c>
+      <c r="C787" s="113" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="789" spans="2:7" ht="29">
+      <c r="C789" s="53" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D789" s="53" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E789" s="53" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F789" s="53" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G789" s="53" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="790" spans="2:7">
+      <c r="C790" s="55" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D790" s="54" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E790" s="54" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F790" s="54" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G790" s="55" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="791" spans="2:7">
+      <c r="C791" s="55" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D791" s="54" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E791" s="54" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F791" s="54" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G791" s="55" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="792" spans="2:7">
+      <c r="C792" s="55" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D792" s="54" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E792" s="54" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F792" s="54" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G792" s="55" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="793" spans="2:7" ht="43.5">
+      <c r="C793" s="55" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D793" s="54" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E793" s="54" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F793" s="54" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G793" s="114">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="794" spans="2:7">
+      <c r="C794" s="55" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D794" s="54" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E794" s="54" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F794" s="54" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G794" s="55" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="795" spans="2:7">
+      <c r="C795" s="55" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D795" s="54" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E795" s="54" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F795" s="54" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G795" s="55" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="796" spans="2:7" ht="29">
+      <c r="C796" s="55" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D796" s="54" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E796" s="54" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F796" s="54" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G796" s="55" t="s">
+        <v>1162</v>
       </c>
     </row>
   </sheetData>
